--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -538,7 +538,7 @@
     <t xml:space="preserve">W18</t>
   </si>
   <si>
-    <t xml:space="preserve">NYY 3x25 mm² Cu</t>
+    <t xml:space="preserve">NYY 3x10 mm² Cu</t>
   </si>
   <si>
     <t xml:space="preserve">W19</t>
@@ -1195,7 +1195,7 @@
     <t xml:space="preserve">NYY 3x2,5 mm² Cu, L=28,0 m</t>
   </si>
   <si>
-    <t xml:space="preserve">NYY 3x25 mm² Cu, L=300,0 m</t>
+    <t xml:space="preserve">NYY 3x10 mm² Cu, L=300,0 m</t>
   </si>
   <si>
     <t xml:space="preserve">W19, W20</t>
@@ -5297,7 +5297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>154</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>167</v>
       </c>
       <c r="J33" s="27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K33" s="27" t="n">
         <v>300</v>
@@ -6143,19 +6143,19 @@
       </c>
       <c r="O33" s="8" t="n">
         <f aca="false">INDEX($X$4:$Z$14,MATCH(J33,$W$4:$W$14,0),MATCH(L33,$X$3:$Z$3,0))</f>
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="P33" s="12" t="n">
         <f aca="false">O33*IF(L33="D2-3",$D$8,$D$7)</f>
-        <v>80.8</v>
+        <v>45.6</v>
       </c>
       <c r="Q33" s="11" t="n">
         <f aca="false">IF(F33="3F",SQRT(3),2)*H33*K33*AA33*(G33/($D$3*J33)+($D$4/1000)*SQRT(1-G33^2))</f>
-        <v>4.45071135511379</v>
+        <v>10.8538734104498</v>
       </c>
       <c r="R33" s="11" t="n">
         <f aca="false">Q33/IF(F33="3F",$D$5,$D$6)*100</f>
-        <v>1.93509189352774</v>
+        <v>4.71907539584772</v>
       </c>
       <c r="S33" s="11" t="n">
         <f aca="false">$R$15</f>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="T33" s="11" t="n">
         <f aca="false">R33+S33</f>
-        <v>2.2073106917826</v>
+        <v>4.99129419410259</v>
       </c>
       <c r="U33" s="11" t="n">
         <f aca="false">IF(D33="aydınlatma",$D$10,$D$9)</f>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V33" s="24" t="str">
         <f aca="false">IF(AND(H33&lt;=N33,N33&lt;=P33,T33&lt;=U33),"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>UYGUN DEĞİL</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>1</v>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="625">
   <si>
     <t xml:space="preserve">YÜK DENGESİ VE FAZ DENGESİZLİĞİ</t>
   </si>
@@ -205,7 +205,19 @@
     <t xml:space="preserve">SS1</t>
   </si>
   <si>
-    <t xml:space="preserve">Ses sistemi</t>
+    <t xml:space="preserve">Ses sistemi - sağ kol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses sistemi - sol kol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses sistemi - minare kol</t>
   </si>
   <si>
     <t xml:space="preserve">AC1</t>
@@ -304,21 +316,21 @@
     <t xml:space="preserve">parametre ile sabit</t>
   </si>
   <si>
+    <t xml:space="preserve">Priz hattı-1 (P1–P10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">en az yüklü faz (grupta farklı faz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priz hattı-2 (P11–P20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priz hattı-3 (P21–P30)</t>
+  </si>
+  <si>
     <t xml:space="preserve">en az yüklü faz</t>
   </si>
   <si>
-    <t xml:space="preserve">Priz hattı-1 (P1–P10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">en az yüklü faz (grupta farklı faz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priz hattı-2 (P11–P20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priz hattı-3 (P21–P30)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Projektör hattı-1 (PR1–PR4)</t>
   </si>
   <si>
@@ -538,16 +550,19 @@
     <t xml:space="preserve">W18</t>
   </si>
   <si>
-    <t xml:space="preserve">NYY 3x10 mm² Cu</t>
-  </si>
-  <si>
     <t xml:space="preserve">W19</t>
   </si>
   <si>
+    <t xml:space="preserve">W20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W21</t>
+  </si>
+  <si>
     <t xml:space="preserve">NHXH FE180/E90 3x2,5 mm² Cu</t>
   </si>
   <si>
-    <t xml:space="preserve">W20</t>
+    <t xml:space="preserve">W22</t>
   </si>
   <si>
     <t xml:space="preserve">Kontroller: Ib ≤ In ≤ Iz(düzeltilmiş) ve toplam ΔU = ΔU hat + ΔU besleme ≤ limit. ΔU = (√3 veya 2)·I·L·(cosφ/(κ·S) + X·sinφ).</t>
@@ -895,6 +910,9 @@
     <t xml:space="preserve">Kamera hattı RCBO</t>
   </si>
   <si>
+    <t xml:space="preserve">SS1–SS3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ses sistemi hattı RCBO</t>
   </si>
   <si>
@@ -1195,10 +1213,13 @@
     <t xml:space="preserve">NYY 3x2,5 mm² Cu, L=28,0 m</t>
   </si>
   <si>
-    <t xml:space="preserve">NYY 3x10 mm² Cu, L=300,0 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W19, W20</t>
+    <t xml:space="preserve">W18–W20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYY 3x2,5 mm² Cu, L=100,0 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W21, W22</t>
   </si>
   <si>
     <t xml:space="preserve">NHXH FE180/E90 3x2,5 mm² Cu, L=35,0 m</t>
@@ -1789,7 +1810,7 @@
     <t xml:space="preserve">MPCB 3P 11-16 A</t>
   </si>
   <si>
-    <t xml:space="preserve">AV1, PZ1–PZ3, LD1–LD3, PJ1–PJ3, KR1, SS1, AC1, YA1</t>
+    <t xml:space="preserve">AV1, PZ1–PZ3, LD1–LD3, PJ1–PJ3, KR1, SS1–SS3, AC1, YA1</t>
   </si>
   <si>
     <t xml:space="preserve">RCBO 1P+N, 30 mA, Tip A</t>
@@ -2430,7 +2451,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -2889,7 +2910,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0.9</v>
@@ -2907,11 +2928,11 @@
       </c>
       <c r="I17" s="11" t="n">
         <f aca="false">IF($D17="3F",$G17/3,IF($D17=I$9,$G17,0))</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J17" s="11" t="n">
         <f aca="false">IF($D17="3F",$G17/3,IF($D17=J$9,$G17,0))</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <f aca="false">IF($D17="3F",$G17*1000/(3*$B$4*$E17),IF($D17=K$9,$G17*1000/($B$4*$E17),0))</f>
@@ -2919,11 +2940,11 @@
       </c>
       <c r="L17" s="12" t="n">
         <f aca="false">IF($D17="3F",$G17*1000/(3*$B$4*$E17),IF($D17=L$9,$G17*1000/($B$4*$E17),0))</f>
-        <v>0</v>
+        <v>7.2463768115942</v>
       </c>
       <c r="M17" s="12" t="n">
         <f aca="false">IF($D17="3F",$G17*1000/(3*$B$4*$E17),IF($D17=M$9,$G17*1000/($B$4*$E17),0))</f>
-        <v>7.2463768115942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2937,7 +2958,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0.9</v>
@@ -2955,11 +2976,11 @@
       </c>
       <c r="I18" s="11" t="n">
         <f aca="false">IF($D18="3F",$G18/3,IF($D18=I$9,$G18,0))</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="11" t="n">
         <f aca="false">IF($D18="3F",$G18/3,IF($D18=J$9,$G18,0))</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K18" s="12" t="n">
         <f aca="false">IF($D18="3F",$G18*1000/(3*$B$4*$E18),IF($D18=K$9,$G18*1000/($B$4*$E18),0))</f>
@@ -2967,11 +2988,11 @@
       </c>
       <c r="L18" s="12" t="n">
         <f aca="false">IF($D18="3F",$G18*1000/(3*$B$4*$E18),IF($D18=L$9,$G18*1000/($B$4*$E18),0))</f>
-        <v>7.2463768115942</v>
+        <v>0</v>
       </c>
       <c r="M18" s="12" t="n">
         <f aca="false">IF($D18="3F",$G18*1000/(3*$B$4*$E18),IF($D18=M$9,$G18*1000/($B$4*$E18),0))</f>
-        <v>0</v>
+        <v>7.2463768115942</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3033,7 +3054,7 @@
         <v>0.255</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>0.9</v>
@@ -3051,11 +3072,11 @@
       </c>
       <c r="I20" s="11" t="n">
         <f aca="false">IF($D20="3F",$G20/3,IF($D20=I$9,$G20,0))</f>
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="J20" s="11" t="n">
         <f aca="false">IF($D20="3F",$G20/3,IF($D20=J$9,$G20,0))</f>
-        <v>0.255</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <f aca="false">IF($D20="3F",$G20*1000/(3*$B$4*$E20),IF($D20=K$9,$G20*1000/($B$4*$E20),0))</f>
@@ -3063,11 +3084,11 @@
       </c>
       <c r="L20" s="12" t="n">
         <f aca="false">IF($D20="3F",$G20*1000/(3*$B$4*$E20),IF($D20=L$9,$G20*1000/($B$4*$E20),0))</f>
-        <v>0</v>
+        <v>1.23188405797101</v>
       </c>
       <c r="M20" s="12" t="n">
         <f aca="false">IF($D20="3F",$G20*1000/(3*$B$4*$E20),IF($D20=M$9,$G20*1000/($B$4*$E20),0))</f>
-        <v>1.23188405797101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3129,7 +3150,7 @@
         <v>0.24</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>0.9</v>
@@ -3147,11 +3168,11 @@
       </c>
       <c r="I22" s="11" t="n">
         <f aca="false">IF($D22="3F",$G22/3,IF($D22=I$9,$G22,0))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">IF($D22="3F",$G22/3,IF($D22=J$9,$G22,0))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K22" s="12" t="n">
         <f aca="false">IF($D22="3F",$G22*1000/(3*$B$4*$E22),IF($D22=K$9,$G22*1000/($B$4*$E22),0))</f>
@@ -3159,11 +3180,11 @@
       </c>
       <c r="L22" s="12" t="n">
         <f aca="false">IF($D22="3F",$G22*1000/(3*$B$4*$E22),IF($D22=L$9,$G22*1000/($B$4*$E22),0))</f>
-        <v>1.15942028985507</v>
+        <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
         <f aca="false">IF($D22="3F",$G22*1000/(3*$B$4*$E22),IF($D22=M$9,$G22*1000/($B$4*$E22),0))</f>
-        <v>0</v>
+        <v>1.15942028985507</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3177,7 +3198,7 @@
         <v>0.4</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>0.9</v>
@@ -3195,11 +3216,11 @@
       </c>
       <c r="I23" s="11" t="n">
         <f aca="false">IF($D23="3F",$G23/3,IF($D23=I$9,$G23,0))</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J23" s="11" t="n">
         <f aca="false">IF($D23="3F",$G23/3,IF($D23=J$9,$G23,0))</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K23" s="12" t="n">
         <f aca="false">IF($D23="3F",$G23*1000/(3*$B$4*$E23),IF($D23=K$9,$G23*1000/($B$4*$E23),0))</f>
@@ -3207,11 +3228,11 @@
       </c>
       <c r="L23" s="12" t="n">
         <f aca="false">IF($D23="3F",$G23*1000/(3*$B$4*$E23),IF($D23=L$9,$G23*1000/($B$4*$E23),0))</f>
-        <v>1.93236714975845</v>
+        <v>0</v>
       </c>
       <c r="M23" s="12" t="n">
         <f aca="false">IF($D23="3F",$G23*1000/(3*$B$4*$E23),IF($D23=M$9,$G23*1000/($B$4*$E23),0))</f>
-        <v>0</v>
+        <v>1.93236714975845</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3225,7 +3246,7 @@
         <v>0.3</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>0.9</v>
@@ -3243,11 +3264,11 @@
       </c>
       <c r="I24" s="11" t="n">
         <f aca="false">IF($D24="3F",$G24/3,IF($D24=I$9,$G24,0))</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J24" s="11" t="n">
         <f aca="false">IF($D24="3F",$G24/3,IF($D24=J$9,$G24,0))</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <f aca="false">IF($D24="3F",$G24*1000/(3*$B$4*$E24),IF($D24=K$9,$G24*1000/($B$4*$E24),0))</f>
@@ -3255,11 +3276,11 @@
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">IF($D24="3F",$G24*1000/(3*$B$4*$E24),IF($D24=L$9,$G24*1000/($B$4*$E24),0))</f>
-        <v>0</v>
+        <v>1.44927536231884</v>
       </c>
       <c r="M24" s="12" t="n">
         <f aca="false">IF($D24="3F",$G24*1000/(3*$B$4*$E24),IF($D24=M$9,$G24*1000/($B$4*$E24),0))</f>
-        <v>1.44927536231884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3321,7 +3342,7 @@
         <v>1.4</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>0.9</v>
@@ -3339,11 +3360,11 @@
       </c>
       <c r="I26" s="11" t="n">
         <f aca="false">IF($D26="3F",$G26/3,IF($D26=I$9,$G26,0))</f>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J26" s="11" t="n">
         <f aca="false">IF($D26="3F",$G26/3,IF($D26=J$9,$G26,0))</f>
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <f aca="false">IF($D26="3F",$G26*1000/(3*$B$4*$E26),IF($D26=K$9,$G26*1000/($B$4*$E26),0))</f>
@@ -3351,11 +3372,11 @@
       </c>
       <c r="L26" s="12" t="n">
         <f aca="false">IF($D26="3F",$G26*1000/(3*$B$4*$E26),IF($D26=L$9,$G26*1000/($B$4*$E26),0))</f>
-        <v>0</v>
+        <v>6.76328502415459</v>
       </c>
       <c r="M26" s="12" t="n">
         <f aca="false">IF($D26="3F",$G26*1000/(3*$B$4*$E26),IF($D26=M$9,$G26*1000/($B$4*$E26),0))</f>
-        <v>6.76328502415459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3366,10 +3387,10 @@
         <v>56</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>0.9</v>
@@ -3379,7 +3400,7 @@
       </c>
       <c r="G27" s="11" t="n">
         <f aca="false">C27*F27</f>
-        <v>1.62</v>
+        <v>0.54</v>
       </c>
       <c r="H27" s="11" t="n">
         <f aca="false">IF($D27="3F",$G27/3,IF($D27=H$9,$G27,0))</f>
@@ -3387,11 +3408,11 @@
       </c>
       <c r="I27" s="11" t="n">
         <f aca="false">IF($D27="3F",$G27/3,IF($D27=I$9,$G27,0))</f>
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="J27" s="11" t="n">
         <f aca="false">IF($D27="3F",$G27/3,IF($D27=J$9,$G27,0))</f>
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="K27" s="12" t="n">
         <f aca="false">IF($D27="3F",$G27*1000/(3*$B$4*$E27),IF($D27=K$9,$G27*1000/($B$4*$E27),0))</f>
@@ -3399,11 +3420,11 @@
       </c>
       <c r="L27" s="12" t="n">
         <f aca="false">IF($D27="3F",$G27*1000/(3*$B$4*$E27),IF($D27=L$9,$G27*1000/($B$4*$E27),0))</f>
-        <v>7.82608695652174</v>
+        <v>0</v>
       </c>
       <c r="M27" s="12" t="n">
         <f aca="false">IF($D27="3F",$G27*1000/(3*$B$4*$E27),IF($D27=M$9,$G27*1000/($B$4*$E27),0))</f>
-        <v>0</v>
+        <v>2.60869565217391</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3414,20 +3435,20 @@
         <v>58</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G28" s="11" t="n">
         <f aca="false">C28*F28</f>
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H28" s="11" t="n">
         <f aca="false">IF($D28="3F",$G28/3,IF($D28=H$9,$G28,0))</f>
@@ -3439,7 +3460,7 @@
       </c>
       <c r="J28" s="11" t="n">
         <f aca="false">IF($D28="3F",$G28/3,IF($D28=J$9,$G28,0))</f>
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="K28" s="12" t="n">
         <f aca="false">IF($D28="3F",$G28*1000/(3*$B$4*$E28),IF($D28=K$9,$G28*1000/($B$4*$E28),0))</f>
@@ -3451,7 +3472,7 @@
       </c>
       <c r="M28" s="12" t="n">
         <f aca="false">IF($D28="3F",$G28*1000/(3*$B$4*$E28),IF($D28=M$9,$G28*1000/($B$4*$E28),0))</f>
-        <v>2.2883295194508</v>
+        <v>2.60869565217391</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3462,20 +3483,20 @@
         <v>60</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G29" s="11" t="n">
         <f aca="false">C29*F29</f>
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="H29" s="11" t="n">
         <f aca="false">IF($D29="3F",$G29/3,IF($D29=H$9,$G29,0))</f>
@@ -3483,11 +3504,11 @@
       </c>
       <c r="I29" s="11" t="n">
         <f aca="false">IF($D29="3F",$G29/3,IF($D29=I$9,$G29,0))</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="11" t="n">
         <f aca="false">IF($D29="3F",$G29/3,IF($D29=J$9,$G29,0))</f>
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="K29" s="12" t="n">
         <f aca="false">IF($D29="3F",$G29*1000/(3*$B$4*$E29),IF($D29=K$9,$G29*1000/($B$4*$E29),0))</f>
@@ -3495,11 +3516,11 @@
       </c>
       <c r="L29" s="12" t="n">
         <f aca="false">IF($D29="3F",$G29*1000/(3*$B$4*$E29),IF($D29=L$9,$G29*1000/($B$4*$E29),0))</f>
-        <v>1.37299771167048</v>
+        <v>0</v>
       </c>
       <c r="M29" s="12" t="n">
         <f aca="false">IF($D29="3F",$G29*1000/(3*$B$4*$E29),IF($D29=M$9,$G29*1000/($B$4*$E29),0))</f>
-        <v>0</v>
+        <v>2.60869565217391</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3510,20 +3531,20 @@
         <v>62</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="11" t="n">
         <f aca="false">C30*F30</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H30" s="11" t="n">
         <f aca="false">IF($D30="3F",$G30/3,IF($D30=H$9,$G30,0))</f>
@@ -3531,7 +3552,7 @@
       </c>
       <c r="I30" s="11" t="n">
         <f aca="false">IF($D30="3F",$G30/3,IF($D30=I$9,$G30,0))</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J30" s="11" t="n">
         <f aca="false">IF($D30="3F",$G30/3,IF($D30=J$9,$G30,0))</f>
@@ -3543,7 +3564,7 @@
       </c>
       <c r="L30" s="12" t="n">
         <f aca="false">IF($D30="3F",$G30*1000/(3*$B$4*$E30),IF($D30=L$9,$G30*1000/($B$4*$E30),0))</f>
-        <v>0</v>
+        <v>2.2883295194508</v>
       </c>
       <c r="M30" s="12" t="n">
         <f aca="false">IF($D30="3F",$G30*1000/(3*$B$4*$E30),IF($D30=M$9,$G30*1000/($B$4*$E30),0))</f>
@@ -3552,26 +3573,26 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="C31" s="9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="11" t="n">
         <f aca="false">C31*F31</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H31" s="11" t="n">
         <f aca="false">IF($D31="3F",$G31/3,IF($D31=H$9,$G31,0))</f>
@@ -3583,7 +3604,7 @@
       </c>
       <c r="J31" s="11" t="n">
         <f aca="false">IF($D31="3F",$G31/3,IF($D31=J$9,$G31,0))</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K31" s="12" t="n">
         <f aca="false">IF($D31="3F",$G31*1000/(3*$B$4*$E31),IF($D31=K$9,$G31*1000/($B$4*$E31),0))</f>
@@ -3595,7 +3616,7 @@
       </c>
       <c r="M31" s="12" t="n">
         <f aca="false">IF($D31="3F",$G31*1000/(3*$B$4*$E31),IF($D31=M$9,$G31*1000/($B$4*$E31),0))</f>
-        <v>0</v>
+        <v>1.37299771167048</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3603,13 +3624,13 @@
         <v>65</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>1</v>
@@ -3647,304 +3668,340 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="16" t="n">
-        <f aca="false">SUM(C10:C32)</f>
+      <c r="C33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <f aca="false">C33*F33</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <f aca="false">IF($D33="3F",$G33/3,IF($D33=H$9,$G33,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <f aca="false">IF($D33="3F",$G33/3,IF($D33=I$9,$G33,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <f aca="false">IF($D33="3F",$G33/3,IF($D33=J$9,$G33,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <f aca="false">IF($D33="3F",$G33*1000/(3*$B$4*$E33),IF($D33=K$9,$G33*1000/($B$4*$E33),0))</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <f aca="false">IF($D33="3F",$G33*1000/(3*$B$4*$E33),IF($D33=L$9,$G33*1000/($B$4*$E33),0))</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <f aca="false">IF($D33="3F",$G33*1000/(3*$B$4*$E33),IF($D33=M$9,$G33*1000/($B$4*$E33),0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <f aca="false">C34*F34</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <f aca="false">IF($D34="3F",$G34/3,IF($D34=H$9,$G34,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <f aca="false">IF($D34="3F",$G34/3,IF($D34=I$9,$G34,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <f aca="false">IF($D34="3F",$G34/3,IF($D34=J$9,$G34,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <f aca="false">IF($D34="3F",$G34*1000/(3*$B$4*$E34),IF($D34=K$9,$G34*1000/($B$4*$E34),0))</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <f aca="false">IF($D34="3F",$G34*1000/(3*$B$4*$E34),IF($D34=L$9,$G34*1000/($B$4*$E34),0))</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <f aca="false">IF($D34="3F",$G34*1000/(3*$B$4*$E34),IF($D34=M$9,$G34*1000/($B$4*$E34),0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="16" t="n">
+        <f aca="false">SUM(C10:C34)</f>
         <v>58.75</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16" t="n">
-        <f aca="false">SUM(G10:G32)</f>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="16" t="n">
+        <f aca="false">SUM(G10:G34)</f>
         <v>51.97</v>
       </c>
-      <c r="H33" s="16" t="n">
-        <f aca="false">SUM(H10:H32)</f>
+      <c r="H35" s="16" t="n">
+        <f aca="false">SUM(H10:H34)</f>
         <v>17.355</v>
       </c>
-      <c r="I33" s="16" t="n">
-        <f aca="false">SUM(I10:I32)</f>
+      <c r="I35" s="16" t="n">
+        <f aca="false">SUM(I10:I34)</f>
+        <v>17.255</v>
+      </c>
+      <c r="J35" s="16" t="n">
+        <f aca="false">SUM(J10:J34)</f>
         <v>17.36</v>
       </c>
-      <c r="J33" s="16" t="n">
-        <f aca="false">SUM(J10:J32)</f>
-        <v>17.255</v>
-      </c>
-      <c r="K33" s="17" t="n">
-        <f aca="false">SUM(K10:K32)</f>
+      <c r="K35" s="17" t="n">
+        <f aca="false">SUM(K10:K34)</f>
         <v>83.3320620391559</v>
       </c>
-      <c r="L33" s="17" t="n">
-        <f aca="false">SUM(L10:L32)</f>
+      <c r="L35" s="17" t="n">
+        <f aca="false">SUM(L10:L34)</f>
+        <v>83.230358504958</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <f aca="false">SUM(M10:M34)</f>
         <v>83.7884566488685</v>
-      </c>
-      <c r="M33" s="17" t="n">
-        <f aca="false">SUM(M10:M32)</f>
-        <v>83.230358504958</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="18" t="n">
-        <f aca="false">C33</f>
-        <v>58.75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="18" t="n">
-        <f aca="false">G33</f>
-        <v>51.97</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B38" s="18" t="n">
-        <f aca="false">(MAX(H33:J33)-MIN(H33:J33))/AVERAGE(H33:J33)*100</f>
-        <v>0.606118914758517</v>
+        <f aca="false">C35</f>
+        <v>58.75</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" s="19" t="str">
-        <f aca="false">IF(B38&lt;=10,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>16</v>
+      </c>
+      <c r="B39" s="18" t="n">
+        <f aca="false">G35</f>
+        <v>51.97</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="20" t="n">
-        <f aca="false">MAX(K33:M33)</f>
-        <v>83.7884566488685</v>
+        <v>72</v>
+      </c>
+      <c r="B40" s="18" t="n">
+        <f aca="false">(MAX(H35:J35)-MIN(H35:J35))/AVERAGE(H35:J35)*100</f>
+        <v>0.606118914758517</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="20" t="n">
-        <f aca="false">AVERAGE(K33:M33)</f>
-        <v>83.4502923976608</v>
+        <v>73</v>
+      </c>
+      <c r="B41" s="19" t="str">
+        <f aca="false">IF(B40&lt;=10,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" s="21" t="n">
-        <f aca="false">G33*1000/(SQRT(3)*B5*AVERAGE(K33:M33))</f>
-        <v>0.898885211414368</v>
+        <v>74</v>
+      </c>
+      <c r="B42" s="20" t="n">
+        <f aca="false">MAX(K35:M35)</f>
+        <v>83.7884566488685</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B43" s="20" t="n">
-        <f aca="false">SQRT(3)*B5*AVERAGE(K33:M33)/1000</f>
-        <v>57.8160585356909</v>
+        <f aca="false">AVERAGE(K35:M35)</f>
+        <v>83.4502923976608</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" s="19" t="str">
-        <f aca="false">IF(B40&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>76</v>
+      </c>
+      <c r="B44" s="21" t="n">
+        <f aca="false">G35*1000/(SQRT(3)*B5*AVERAGE(K35:M35))</f>
+        <v>0.898885211414368</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B45" s="20" t="n">
-        <f aca="false">B43/250*100</f>
-        <v>23.1264234142764</v>
+        <f aca="false">SQRT(3)*B5*AVERAGE(K35:M35)/1000</f>
+        <v>57.8160585356909</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B46" s="20" t="n">
-        <f aca="false">B40*(1+B7/100)</f>
-        <v>104.735570811086</v>
+        <v>78</v>
+      </c>
+      <c r="B46" s="19" t="str">
+        <f aca="false">IF(B42&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B47" s="19" t="str">
-        <f aca="false">IF(B46&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>79</v>
+      </c>
+      <c r="B47" s="20" t="n">
+        <f aca="false">B45/250*100</f>
+        <v>23.1264234142764</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B48" s="20" t="n">
-        <f aca="false">(B6-B40)/B6*100</f>
-        <v>47.6322145944572</v>
+        <f aca="false">B42*(1+B7/100)</f>
+        <v>104.735570811086</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="19" t="str">
+        <f aca="false">IF(B48&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="20" t="n">
+        <f aca="false">(B6-B42)/B6*100</f>
+        <v>47.6322145944572</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D53" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J51" s="7" t="s">
+      <c r="E53" s="7" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="8" t="s">
+      <c r="F53" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D52" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52" s="8" t="s">
+      <c r="G53" s="7"/>
+      <c r="H53" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G52" s="8"/>
-      <c r="H52" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E53" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="8" t="s">
+      <c r="I53" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G53" s="8"/>
-      <c r="H53" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>0</v>
+      <c r="J53" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D54" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D55" s="23" t="n">
         <v>1.5</v>
@@ -3953,44 +4010,44 @@
         <v>18</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="11" t="n">
         <v>2</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>3.12</v>
+        <v>1.5</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D56" s="23" t="n">
         <v>1.5</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="11" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>3.12</v>
+        <v>1.5</v>
       </c>
       <c r="J56" s="11" t="n">
         <v>1.5</v>
@@ -3998,286 +4055,404 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="D57" s="23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>3.12</v>
+        <v>1.5</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>19</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E62" s="24" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D63" s="23" t="n">
-        <v>0.255</v>
+        <v>0.4</v>
       </c>
       <c r="E63" s="24" t="s">
         <v>19</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>3.955</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D64" s="23" t="n">
-        <v>0.255</v>
+        <v>0.3</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G64" s="8"/>
       <c r="H64" s="11" t="n">
-        <v>4.055</v>
+        <v>3.5</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>3.955</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D65" s="23" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G66" s="8"/>
+      <c r="H66" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J66" s="11" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G67" s="8"/>
+      <c r="H67" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G68" s="8"/>
+      <c r="H68" s="11" t="n">
         <v>4.055</v>
       </c>
-      <c r="I65" s="11" t="n">
+      <c r="I68" s="11" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="J68" s="11" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D69" s="23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" s="8"/>
+      <c r="H69" s="11" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="J69" s="11" t="n">
         <v>4.06</v>
       </c>
-      <c r="J65" s="11" t="n">
-        <v>3.955</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="25" t="s">
-        <v>100</v>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="25" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="K8:M8"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="F54:G54"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="F56:G56"/>
@@ -4290,6 +4465,10 @@
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="F64:G64"/>
     <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F69:G69"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4306,7 +4485,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AA38"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
@@ -4336,7 +4515,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,12 +4523,12 @@
         <v>1</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4357,21 +4536,21 @@
         <v>44</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4437,7 +4616,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4459,7 +4638,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4481,7 +4660,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4503,7 +4682,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4525,7 +4704,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4575,70 +4754,70 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="W14" s="12" t="n">
         <v>95</v>
@@ -4653,39 +4832,39 @@
         <v>216</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E15" s="11" t="n">
-        <f aca="false">'Yük Dengesi'!B37</f>
+        <f aca="false">'Yük Dengesi'!B39</f>
         <v>51.97</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="23" t="n">
+        <f aca="false">'Yük Dengesi'!B44</f>
+        <v>0.898885211414368</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <f aca="false">'Yük Dengesi'!B42</f>
-        <v>0.898885211414368</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <f aca="false">'Yük Dengesi'!B40</f>
         <v>83.7884566488685</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J15" s="27" t="n">
         <v>95</v>
@@ -4694,10 +4873,10 @@
         <v>30</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>160</v>
@@ -4739,7 +4918,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
@@ -4748,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
@@ -4764,7 +4943,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>4</v>
@@ -4773,10 +4952,10 @@
         <v>25</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>14</v>
@@ -4819,7 +4998,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>23</v>
@@ -4828,7 +5007,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
@@ -4844,7 +5023,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J17" s="27" t="n">
         <v>4</v>
@@ -4853,10 +5032,10 @@
         <v>25</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>14</v>
@@ -4899,7 +5078,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
@@ -4908,7 +5087,7 @@
         <v>26</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
@@ -4924,7 +5103,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>4</v>
@@ -4933,10 +5112,10 @@
         <v>25</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>14</v>
@@ -4979,7 +5158,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>27</v>
@@ -4988,7 +5167,7 @@
         <v>28</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
@@ -5004,7 +5183,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J19" s="27" t="n">
         <v>4</v>
@@ -5013,10 +5192,10 @@
         <v>25</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>14</v>
@@ -5059,7 +5238,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
@@ -5068,7 +5247,7 @@
         <v>30</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
@@ -5084,7 +5263,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>4</v>
@@ -5093,10 +5272,10 @@
         <v>25</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>14</v>
@@ -5139,7 +5318,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -5148,7 +5327,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
@@ -5164,7 +5343,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J21" s="27" t="n">
         <v>4</v>
@@ -5173,10 +5352,10 @@
         <v>25</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>14</v>
@@ -5219,7 +5398,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>33</v>
@@ -5228,13 +5407,13 @@
         <v>34</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0.95</v>
@@ -5244,7 +5423,7 @@
         <v>9.1533180778032</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>16</v>
@@ -5253,10 +5432,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>16</v>
@@ -5297,9 +5476,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>35</v>
@@ -5308,13 +5487,13 @@
         <v>36</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0.9</v>
@@ -5324,7 +5503,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J23" s="27" t="n">
         <v>16</v>
@@ -5333,10 +5512,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>16</v>
@@ -5379,7 +5558,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>37</v>
@@ -5388,13 +5567,13 @@
         <v>38</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0.9</v>
@@ -5404,7 +5583,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>16</v>
@@ -5413,10 +5592,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>16</v>
@@ -5459,7 +5638,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -5468,13 +5647,13 @@
         <v>40</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0.9</v>
@@ -5484,7 +5663,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J25" s="27" t="n">
         <v>16</v>
@@ -5493,10 +5672,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>16</v>
@@ -5539,7 +5718,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>41</v>
@@ -5548,13 +5727,13 @@
         <v>42</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>0.255</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0.9</v>
@@ -5564,7 +5743,7 @@
         <v>1.23188405797101</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>2.5</v>
@@ -5573,10 +5752,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>10</v>
@@ -5619,7 +5798,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>43</v>
@@ -5628,13 +5807,13 @@
         <v>44</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>0.255</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0.9</v>
@@ -5644,7 +5823,7 @@
         <v>1.23188405797101</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J27" s="27" t="n">
         <v>2.5</v>
@@ -5653,10 +5832,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>10</v>
@@ -5699,7 +5878,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>45</v>
@@ -5708,13 +5887,13 @@
         <v>46</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0.24</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0.9</v>
@@ -5724,7 +5903,7 @@
         <v>1.15942028985507</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>2.5</v>
@@ -5733,10 +5912,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>10</v>
@@ -5779,7 +5958,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>47</v>
@@ -5788,13 +5967,13 @@
         <v>48</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0.9</v>
@@ -5804,7 +5983,7 @@
         <v>1.93236714975845</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J29" s="27" t="n">
         <v>2.5</v>
@@ -5813,10 +5992,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>10</v>
@@ -5859,7 +6038,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>49</v>
@@ -5868,13 +6047,13 @@
         <v>50</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0.9</v>
@@ -5884,7 +6063,7 @@
         <v>1.44927536231884</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>2.5</v>
@@ -5893,10 +6072,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>10</v>
@@ -5939,7 +6118,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>51</v>
@@ -5948,13 +6127,13 @@
         <v>52</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0.9</v>
@@ -5964,7 +6143,7 @@
         <v>1.44927536231884</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J31" s="27" t="n">
         <v>2.5</v>
@@ -5973,10 +6152,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>10</v>
@@ -6019,7 +6198,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>53</v>
@@ -6028,13 +6207,13 @@
         <v>54</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.9</v>
@@ -6044,7 +6223,7 @@
         <v>6.76328502415459</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>2.5</v>
@@ -6053,10 +6232,10 @@
         <v>28</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>10</v>
@@ -6099,7 +6278,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>55</v>
@@ -6108,54 +6287,54 @@
         <v>56</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="H33" s="11" t="n">
         <f aca="false">IF(F33="3F",E33*1000/(SQRT(3)*$D$5*G33),E33*1000/($D$6*G33))</f>
-        <v>8.69565217391304</v>
+        <v>2.89855072463768</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J33" s="27" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>10</v>
       </c>
       <c r="O33" s="8" t="n">
         <f aca="false">INDEX($X$4:$Z$14,MATCH(J33,$W$4:$W$14,0),MATCH(L33,$X$3:$Z$3,0))</f>
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="P33" s="12" t="n">
         <f aca="false">O33*IF(L33="D2-3",$D$8,$D$7)</f>
-        <v>45.6</v>
+        <v>19.2</v>
       </c>
       <c r="Q33" s="11" t="n">
         <f aca="false">IF(F33="3F",SQRT(3),2)*H33*K33*AA33*(G33/($D$3*J33)+($D$4/1000)*SQRT(1-G33^2))</f>
-        <v>10.8538734104498</v>
+        <v>4.76329818745885</v>
       </c>
       <c r="R33" s="11" t="n">
         <f aca="false">Q33/IF(F33="3F",$D$5,$D$6)*100</f>
-        <v>4.71907539584772</v>
+        <v>2.07099921193863</v>
       </c>
       <c r="S33" s="11" t="n">
         <f aca="false">$R$15</f>
@@ -6163,7 +6342,7 @@
       </c>
       <c r="T33" s="11" t="n">
         <f aca="false">R33+S33</f>
-        <v>4.99129419410259</v>
+        <v>2.34321801019349</v>
       </c>
       <c r="U33" s="11" t="n">
         <f aca="false">IF(D33="aydınlatma",$D$10,$D$9)</f>
@@ -6171,7 +6350,7 @@
       </c>
       <c r="V33" s="24" t="str">
         <f aca="false">IF(AND(H33&lt;=N33,N33&lt;=P33,T33&lt;=U33),"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN DEĞİL</v>
+        <v>UYGUN</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>1</v>
@@ -6179,7 +6358,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>57</v>
@@ -6188,35 +6367,35 @@
         <v>58</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H34" s="11" t="n">
         <f aca="false">IF(F34="3F",E34*1000/(SQRT(3)*$D$5*G34),E34*1000/($D$6*G34))</f>
-        <v>2.2883295194508</v>
+        <v>2.89855072463768</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>10</v>
@@ -6231,11 +6410,11 @@
       </c>
       <c r="Q34" s="11" t="n">
         <f aca="false">IF(F34="3F",SQRT(3),2)*H34*K34*AA34*(G34/($D$3*J34)+($D$4/1000)*SQRT(1-G34^2))</f>
-        <v>1.38740058120139</v>
+        <v>4.76329818745885</v>
       </c>
       <c r="R34" s="11" t="n">
         <f aca="false">Q34/IF(F34="3F",$D$5,$D$6)*100</f>
-        <v>0.603217644000603</v>
+        <v>2.07099921193863</v>
       </c>
       <c r="S34" s="11" t="n">
         <f aca="false">$R$15</f>
@@ -6243,11 +6422,11 @@
       </c>
       <c r="T34" s="11" t="n">
         <f aca="false">R34+S34</f>
-        <v>0.875436442255466</v>
+        <v>2.34321801019349</v>
       </c>
       <c r="U34" s="11" t="n">
         <f aca="false">IF(D34="aydınlatma",$D$10,$D$9)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V34" s="24" t="str">
         <f aca="false">IF(AND(H34&lt;=N34,N34&lt;=P34,T34&lt;=U34),"UYGUN","UYGUN DEĞİL")</f>
@@ -6259,7 +6438,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>59</v>
@@ -6268,35 +6447,35 @@
         <v>60</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H35" s="11" t="n">
         <f aca="false">IF(F35="3F",E35*1000/(SQRT(3)*$D$5*G35),E35*1000/($D$6*G35))</f>
-        <v>1.37299771167048</v>
+        <v>2.89855072463768</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="K35" s="27" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>10</v>
@@ -6311,11 +6490,11 @@
       </c>
       <c r="Q35" s="11" t="n">
         <f aca="false">IF(F35="3F",SQRT(3),2)*H35*K35*AA35*(G35/($D$3*J35)+($D$4/1000)*SQRT(1-G35^2))</f>
-        <v>0.832440348720832</v>
+        <v>4.76329818745885</v>
       </c>
       <c r="R35" s="11" t="n">
         <f aca="false">Q35/IF(F35="3F",$D$5,$D$6)*100</f>
-        <v>0.361930586400362</v>
+        <v>2.07099921193863</v>
       </c>
       <c r="S35" s="11" t="n">
         <f aca="false">$R$15</f>
@@ -6323,7 +6502,7 @@
       </c>
       <c r="T35" s="11" t="n">
         <f aca="false">R35+S35</f>
-        <v>0.634149384655224</v>
+        <v>2.34321801019349</v>
       </c>
       <c r="U35" s="11" t="n">
         <f aca="false">IF(D35="aydınlatma",$D$10,$D$9)</f>
@@ -6337,14 +6516,174 @@
         <v>1</v>
       </c>
     </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <f aca="false">IF(F36="3F",E36*1000/(SQRT(3)*$D$5*G36),E36*1000/($D$6*G36))</f>
+        <v>2.2883295194508</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <f aca="false">INDEX($X$4:$Z$14,MATCH(J36,$W$4:$W$14,0),MATCH(L36,$X$3:$Z$3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="P36" s="12" t="n">
+        <f aca="false">O36*IF(L36="D2-3",$D$8,$D$7)</f>
+        <v>19.2</v>
+      </c>
+      <c r="Q36" s="11" t="n">
+        <f aca="false">IF(F36="3F",SQRT(3),2)*H36*K36*AA36*(G36/($D$3*J36)+($D$4/1000)*SQRT(1-G36^2))</f>
+        <v>1.38740058120139</v>
+      </c>
+      <c r="R36" s="11" t="n">
+        <f aca="false">Q36/IF(F36="3F",$D$5,$D$6)*100</f>
+        <v>0.603217644000603</v>
+      </c>
+      <c r="S36" s="11" t="n">
+        <f aca="false">$R$15</f>
+        <v>0.272218798254863</v>
+      </c>
+      <c r="T36" s="11" t="n">
+        <f aca="false">R36+S36</f>
+        <v>0.875436442255466</v>
+      </c>
+      <c r="U36" s="11" t="n">
+        <f aca="false">IF(D36="aydınlatma",$D$10,$D$9)</f>
+        <v>2</v>
+      </c>
+      <c r="V36" s="24" t="str">
+        <f aca="false">IF(AND(H36&lt;=N36,N36&lt;=P36,T36&lt;=U36),"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="AA36" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="s">
-        <v>172</v>
+      <c r="A37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <f aca="false">IF(F37="3F",E37*1000/(SQRT(3)*$D$5*G37),E37*1000/($D$6*G37))</f>
+        <v>1.37299771167048</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="J37" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K37" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <f aca="false">INDEX($X$4:$Z$14,MATCH(J37,$W$4:$W$14,0),MATCH(L37,$X$3:$Z$3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <f aca="false">O37*IF(L37="D2-3",$D$8,$D$7)</f>
+        <v>19.2</v>
+      </c>
+      <c r="Q37" s="11" t="n">
+        <f aca="false">IF(F37="3F",SQRT(3),2)*H37*K37*AA37*(G37/($D$3*J37)+($D$4/1000)*SQRT(1-G37^2))</f>
+        <v>0.832440348720832</v>
+      </c>
+      <c r="R37" s="11" t="n">
+        <f aca="false">Q37/IF(F37="3F",$D$5,$D$6)*100</f>
+        <v>0.361930586400362</v>
+      </c>
+      <c r="S37" s="11" t="n">
+        <f aca="false">$R$15</f>
+        <v>0.272218798254863</v>
+      </c>
+      <c r="T37" s="11" t="n">
+        <f aca="false">R37+S37</f>
+        <v>0.634149384655224</v>
+      </c>
+      <c r="U37" s="11" t="n">
+        <f aca="false">IF(D37="aydınlatma",$D$10,$D$9)</f>
+        <v>3</v>
+      </c>
+      <c r="V37" s="24" t="str">
+        <f aca="false">IF(AND(H37&lt;=N37,N37&lt;=P37,T37&lt;=U37),"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="AA37" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="25" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6387,7 +6726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6400,24 +6739,24 @@
         <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -6427,622 +6766,622 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C8" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C14" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C15" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C16" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C17" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C18" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C21" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C23" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C24" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C27" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C31" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C32" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C33" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C34" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C35" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C36" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7050,79 +7389,79 @@
         <v>33</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C37" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C38" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>281</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C40" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7130,244 +7469,244 @@
         <v>53</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C41" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>55</v>
+        <v>291</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C42" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C43" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C44" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C45" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C46" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C47" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>301</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C48" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C50" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C51" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="28" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C52" s="22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -7377,562 +7716,562 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C54" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C55" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="28" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="F56" s="22" t="s">
         <v>328</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="28" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C57" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C58" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="28" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C59" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D59" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="F59" s="22" t="s">
         <v>338</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="28" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C60" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C61" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="28" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C62" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="28" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C63" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="28" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C64" s="22" t="n">
         <v>17</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C65" s="22" t="n">
         <v>17</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C66" s="22" t="n">
         <v>16</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C67" s="22" t="n">
         <v>4</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="28" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C68" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="28" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C69" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="28" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C70" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="28" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C71" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="28" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C72" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="28" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C73" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="28" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C74" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="28" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C75" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="28" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C76" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="28" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C77" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="28" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C78" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C79" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="28" t="s">
-        <v>166</v>
+        <v>392</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C80" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C81" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F81" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -7971,7 +8310,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7981,7 +8320,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -7993,36 +8332,36 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1</v>
@@ -8041,18 +8380,18 @@
         <v>17</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>10</v>
@@ -8068,21 +8407,21 @@
         <v>35</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>10</v>
@@ -8098,21 +8437,21 @@
         <v>37</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>10</v>
@@ -8131,18 +8470,18 @@
         <v>17</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>17</v>
@@ -8158,21 +8497,21 @@
         <v>41</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>17</v>
@@ -8191,18 +8530,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>16</v>
@@ -8218,21 +8557,21 @@
         <v>45</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>4</v>
@@ -8248,21 +8587,21 @@
         <v>47</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>3</v>
@@ -8278,21 +8617,21 @@
         <v>49</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>3</v>
@@ -8311,15 +8650,15 @@
         <v>17</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="32" t="n">
@@ -8338,7 +8677,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -8351,10 +8690,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>1</v>
@@ -8365,21 +8704,21 @@
         <v>47</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>1</v>
@@ -8390,21 +8729,21 @@
         <v>49</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>1</v>
@@ -8418,46 +8757,46 @@
         <v>17</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">ROUNDUP(('Kablo Çizelgesi'!K29+'Kablo Çizelgesi'!K30+'Kablo Çizelgesi'!K31)*(1+$C$3/100),0)</f>
         <v>220</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="22" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
@@ -8465,16 +8804,16 @@
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -8510,7 +8849,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8520,7 +8859,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8529,7 +8868,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="n">
@@ -8538,7 +8877,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="n">
@@ -8547,7 +8886,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="n">
@@ -8556,7 +8895,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="n">
@@ -8565,7 +8904,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="n">
@@ -8574,7 +8913,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="n">
@@ -8583,7 +8922,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="n">
@@ -8592,7 +8931,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="n">
@@ -8601,7 +8940,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="n">
@@ -8610,7 +8949,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="n">
@@ -8619,7 +8958,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="n">
@@ -8628,7 +8967,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="n">
@@ -8637,7 +8976,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="n">
@@ -8646,7 +8985,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="n">
@@ -8655,7 +8994,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="n">
@@ -8664,7 +9003,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="n">
@@ -8673,7 +9012,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="n">
@@ -8682,7 +9021,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
@@ -8691,7 +9030,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="n">
@@ -8700,7 +9039,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="n">
@@ -8709,7 +9048,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="n">
@@ -8718,7 +9057,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="n">
@@ -8730,516 +9069,516 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D28" s="33" t="n">
         <f aca="false">2*(($C$3+2*$C$5)+($C$4+2*$C$5))</f>
         <v>88</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D29" s="33" t="n">
         <f aca="false">ROUNDUP(D28*(1+$C$10/100),0)</f>
         <v>97</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D30" s="33" t="n">
         <f aca="false">2*(ROUNDUP(($C$3+2*$C$5)/$C$8,0)+ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>12</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D31" s="33" t="n">
         <f aca="false">D30*$C$7</f>
         <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">MAX(($C$3+2*$C$5)/ROUNDUP(($C$3+2*$C$5)/$C$8,0),($C$4+2*$C$5)/ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>7.33333333333333</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D33" s="33" t="n">
         <f aca="false">$C$15</f>
         <v>4</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D34" s="33" t="n">
         <f aca="false">MIN(8,MAX(2,ROUNDUP(2*($C$3+$C$4)/$C$9,0)))</f>
         <v>6</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D35" s="33" t="n">
         <f aca="false">D34</f>
         <v>6</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D36" s="33" t="n">
         <f aca="false">ROUNDUP((D34*($C$11+$C$6)+($C$13-$C$11)+(PI()*$C$14/2+2))*(1+$C$10/100),0)</f>
         <v>101</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D37" s="33" t="n">
         <f aca="false">ROUNDUP((2*($C$3+$C$4)+$C$4/2+3)*(1+$C$10/100),0)</f>
         <v>103</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D38" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">$C$23+$C$24+$C$25</f>
         <v>4.5</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D40" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D41" s="33" t="n">
         <f aca="false">ROUNDUP($C$16*(1+$C$10/100),0)</f>
         <v>3</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D42" s="33" t="n">
         <f aca="false">ROUNDUP($C$17*(1+$C$10/100),0)</f>
         <v>4</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D43" s="33" t="n">
         <f aca="false">ROUNDUP($C$22*(1+$C$10/100),0)</f>
         <v>33</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D44" s="33" t="n">
         <f aca="false">$C$18</f>
         <v>3</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D45" s="33" t="n">
         <f aca="false">($C$18-1)*$C$19+6</f>
         <v>18</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D46" s="33" t="n">
         <f aca="false">ROUNDUP($C$21*$C$20*(1+$C$10/100),0)</f>
         <v>80</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D48" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
         <v>27</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D50" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D51" s="33" t="n">
         <f aca="false">ROUNDUP(D49/10,0)</f>
         <v>3</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -9301,7 +9640,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9311,7 +9650,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9331,7 +9670,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9341,7 +9680,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9351,7 +9690,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -9361,7 +9700,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -9371,7 +9710,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -9381,7 +9720,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9391,7 +9730,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -9411,7 +9750,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9421,7 +9760,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -9431,7 +9770,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -9441,7 +9780,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -9451,7 +9790,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -9461,7 +9800,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -9471,7 +9810,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -9481,7 +9820,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -9491,7 +9830,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -9505,7 +9844,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -9514,12 +9853,12 @@
         <v>360.843918243516</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -9528,12 +9867,12 @@
         <v>9.0210979560879</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -9542,12 +9881,12 @@
         <v>0.0256</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -9556,12 +9895,12 @@
         <v>0.00832</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -9570,12 +9909,12 @@
         <v>0.0242102788088035</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -9584,12 +9923,12 @@
         <v>0.0056390977443609</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -9598,12 +9937,12 @@
         <v>0.0024</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -9612,12 +9951,12 @@
         <v>0.0300493485473292</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -9626,12 +9965,12 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -9645,52 +9984,52 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">$D$12</f>
         <v>160</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F35" s="22" t="n">
         <f aca="false">$D$14</f>
@@ -9709,21 +10048,21 @@
         <v>UYGUN</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">$D$15</f>
@@ -9746,24 +10085,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>63</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F37" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -9781,24 +10120,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>25</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F38" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -9816,27 +10155,27 @@
         <v>UYGUN</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="D39" s="22" t="n">
         <v>25</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G39" s="22" t="n">
         <v>10</v>
@@ -9850,18 +10189,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>63</v>
@@ -9884,24 +10223,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F41" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -9922,16 +10261,16 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="E42" s="22" t="n">
         <v>30</v>
@@ -9951,15 +10290,15 @@
         <v>UYGUN</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="G43" s="8" t="n">
         <f aca="false">$D$10</f>
@@ -9976,7 +10315,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -9990,42 +10329,42 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="C47" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10060,10 +10399,10 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C48" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10098,7 +10437,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -10112,29 +10451,29 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -10143,15 +10482,15 @@
         <v>960</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -10160,19 +10499,19 @@
         <v>100</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="F53" s="24" t="str">
         <f aca="false">IF(D53&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -10181,19 +10520,19 @@
         <v>10</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F54" s="24" t="str">
         <f aca="false">IF(D54&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -10202,20 +10541,20 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="639">
   <si>
     <t xml:space="preserve">YÜK DENGESİ VE FAZ DENGESİZLİĞİ</t>
   </si>
@@ -331,6 +331,12 @@
     <t xml:space="preserve">en az yüklü faz</t>
   </si>
   <si>
+    <t xml:space="preserve">Ses sistemi - sağ kol + SS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">en az yüklü faz (SS2 aynı ortak RCD altında, aynı faz)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Projektör hattı-1 (PR1–PR4)</t>
   </si>
   <si>
@@ -550,6 +556,9 @@
     <t xml:space="preserve">W18</t>
   </si>
   <si>
+    <t xml:space="preserve">MCB 1P+N C10 (RCD3 altında)</t>
+  </si>
+  <si>
     <t xml:space="preserve">W19</t>
   </si>
   <si>
@@ -874,6 +883,15 @@
     <t xml:space="preserve">3P MPCB 11-16 A (ayar 14 A), Icu=50 kA; alternatif C20</t>
   </si>
   <si>
+    <t xml:space="preserve">RCD3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses sistemi ortak kaçak akım rölesi (RCD 2P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2P 25 A, 30 mA, Tip A, Inc=10 kA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Avize hattı RCBO</t>
   </si>
   <si>
@@ -910,7 +928,13 @@
     <t xml:space="preserve">Kamera hattı RCBO</t>
   </si>
   <si>
-    <t xml:space="preserve">SS1–SS3</t>
+    <t xml:space="preserve">SS1, SS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses sistemi hattı MCB (RCD3 altında)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1P+N C10 A, 10 kA</t>
   </si>
   <si>
     <t xml:space="preserve">Ses sistemi hattı RCBO</t>
@@ -1810,7 +1834,7 @@
     <t xml:space="preserve">MPCB 3P 11-16 A</t>
   </si>
   <si>
-    <t xml:space="preserve">AV1, PZ1–PZ3, LD1–LD3, PJ1–PJ3, KR1, SS1–SS3, AC1, YA1</t>
+    <t xml:space="preserve">AV1, PZ1–PZ3, LD1–LD3, PJ1–PJ3, KR1, SS3, AC1, YA1</t>
   </si>
   <si>
     <t xml:space="preserve">RCBO 1P+N, 30 mA, Tip A</t>
@@ -1822,6 +1846,21 @@
     <t xml:space="preserve">6 kA yetmez: Ik &gt; 6 kA; LED hatlarında C eğrisi (inrush)</t>
   </si>
   <si>
+    <t xml:space="preserve">RCD 2P 25 A, 30 mA, Tip A (ses ortak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inc: altındaki MCB'lerle birlikte yedek koruma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCB 1P+N C10 A (RCD3 altında)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses kolları aşırı akım koruması</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q0 ≥ 25 kA şartı</t>
   </si>
   <si>
@@ -1865,6 +1904,9 @@
   </si>
   <si>
     <t xml:space="preserve">RCBO (AY, PR, KR, SS, AC, YA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCD3 (ses ortak)</t>
   </si>
   <si>
     <t xml:space="preserve">D) AŞIRI AKIM SEÇİCİLİĞİ (Q0 zaman gecikmeli, alt kademeler anlık)</t>
@@ -2451,7 +2493,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -4121,16 +4163,16 @@
         <v>55</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>19</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="11" t="n">
@@ -4140,18 +4182,18 @@
         <v>2.9</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D60" s="23" t="n">
         <v>0.54</v>
@@ -4170,24 +4212,24 @@
         <v>2.9</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>97</v>
@@ -4197,7 +4239,7 @@
         <v>3.5</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J61" s="11" t="n">
         <v>3.12</v>
@@ -4205,22 +4247,22 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="11" t="n">
@@ -4230,24 +4272,24 @@
         <v>3.4</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>3.12</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D63" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>94</v>
@@ -4257,7 +4299,7 @@
         <v>3.5</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J63" s="11" t="n">
         <v>3.52</v>
@@ -4265,26 +4307,26 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D64" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>94</v>
       </c>
       <c r="G64" s="8"/>
       <c r="H64" s="11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I64" s="11" t="n">
         <v>3.7</v>
@@ -4295,22 +4337,22 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D65" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="11" t="n">
@@ -4320,34 +4362,34 @@
         <v>3.7</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D66" s="23" t="n">
-        <v>0.3</v>
+        <v>0.255</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="11" t="n">
         <v>3.8</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>3.7</v>
+        <v>3.955</v>
       </c>
       <c r="J66" s="11" t="n">
         <v>3.82</v>
@@ -4355,26 +4397,26 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D67" s="23" t="n">
         <v>0.255</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>94</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="11" t="n">
-        <v>3.8</v>
+        <v>4.055</v>
       </c>
       <c r="I67" s="11" t="n">
         <v>3.955</v>
@@ -4385,19 +4427,19 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D68" s="23" t="n">
-        <v>0.255</v>
+        <v>0.24</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>94</v>
@@ -4410,46 +4452,16 @@
         <v>3.955</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>3.82</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" s="23" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G69" s="8"/>
-      <c r="H69" s="11" t="n">
-        <v>4.055</v>
-      </c>
-      <c r="I69" s="11" t="n">
-        <v>3.955</v>
-      </c>
-      <c r="J69" s="11" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="25" t="s">
-        <v>104</v>
+      <c r="A69" s="25" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="A37:C37"/>
@@ -4468,7 +4480,6 @@
     <mergeCell ref="F66:G66"/>
     <mergeCell ref="F67:G67"/>
     <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F69:G69"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4515,7 +4526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4523,12 +4534,12 @@
         <v>1</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4536,21 +4547,21 @@
         <v>44</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4616,7 +4627,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4638,7 +4649,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4660,7 +4671,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4682,7 +4693,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4704,7 +4715,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4754,70 +4765,70 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="W14" s="12" t="n">
         <v>95</v>
@@ -4832,21 +4843,21 @@
         <v>216</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E15" s="11" t="n">
         <f aca="false">'Yük Dengesi'!B39</f>
@@ -4864,7 +4875,7 @@
         <v>83.7884566488685</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J15" s="27" t="n">
         <v>95</v>
@@ -4873,10 +4884,10 @@
         <v>30</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>160</v>
@@ -4918,7 +4929,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
@@ -4927,7 +4938,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
@@ -4943,7 +4954,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>4</v>
@@ -4952,10 +4963,10 @@
         <v>25</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>14</v>
@@ -4998,7 +5009,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>23</v>
@@ -5007,7 +5018,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
@@ -5023,7 +5034,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J17" s="27" t="n">
         <v>4</v>
@@ -5032,10 +5043,10 @@
         <v>25</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>14</v>
@@ -5078,7 +5089,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
@@ -5087,7 +5098,7 @@
         <v>26</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
@@ -5103,7 +5114,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>4</v>
@@ -5112,10 +5123,10 @@
         <v>25</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>14</v>
@@ -5158,7 +5169,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>27</v>
@@ -5167,7 +5178,7 @@
         <v>28</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
@@ -5183,7 +5194,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J19" s="27" t="n">
         <v>4</v>
@@ -5192,10 +5203,10 @@
         <v>25</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>14</v>
@@ -5238,7 +5249,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
@@ -5247,7 +5258,7 @@
         <v>30</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
@@ -5263,7 +5274,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>4</v>
@@ -5272,10 +5283,10 @@
         <v>25</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>14</v>
@@ -5318,7 +5329,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -5327,7 +5338,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
@@ -5343,7 +5354,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J21" s="27" t="n">
         <v>4</v>
@@ -5352,10 +5363,10 @@
         <v>25</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>14</v>
@@ -5398,7 +5409,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>33</v>
@@ -5407,13 +5418,13 @@
         <v>34</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0.95</v>
@@ -5423,7 +5434,7 @@
         <v>9.1533180778032</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>16</v>
@@ -5432,10 +5443,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>16</v>
@@ -5478,7 +5489,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>35</v>
@@ -5487,13 +5498,13 @@
         <v>36</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0.9</v>
@@ -5503,7 +5514,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J23" s="27" t="n">
         <v>16</v>
@@ -5512,10 +5523,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>16</v>
@@ -5558,7 +5569,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>37</v>
@@ -5567,13 +5578,13 @@
         <v>38</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0.9</v>
@@ -5583,7 +5594,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>16</v>
@@ -5592,10 +5603,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>16</v>
@@ -5638,7 +5649,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -5647,13 +5658,13 @@
         <v>40</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0.9</v>
@@ -5663,7 +5674,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="27" t="n">
         <v>16</v>
@@ -5672,10 +5683,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>16</v>
@@ -5718,7 +5729,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>41</v>
@@ -5727,13 +5738,13 @@
         <v>42</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>0.255</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0.9</v>
@@ -5743,7 +5754,7 @@
         <v>1.23188405797101</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>2.5</v>
@@ -5752,10 +5763,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>10</v>
@@ -5798,7 +5809,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>43</v>
@@ -5807,13 +5818,13 @@
         <v>44</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>0.255</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0.9</v>
@@ -5823,7 +5834,7 @@
         <v>1.23188405797101</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J27" s="27" t="n">
         <v>2.5</v>
@@ -5832,10 +5843,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>10</v>
@@ -5878,7 +5889,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>45</v>
@@ -5887,13 +5898,13 @@
         <v>46</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0.24</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0.9</v>
@@ -5903,7 +5914,7 @@
         <v>1.15942028985507</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>2.5</v>
@@ -5912,10 +5923,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>10</v>
@@ -5958,7 +5969,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>47</v>
@@ -5967,13 +5978,13 @@
         <v>48</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0.9</v>
@@ -5983,7 +5994,7 @@
         <v>1.93236714975845</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J29" s="27" t="n">
         <v>2.5</v>
@@ -5992,10 +6003,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>10</v>
@@ -6038,7 +6049,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>49</v>
@@ -6047,13 +6058,13 @@
         <v>50</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0.9</v>
@@ -6063,7 +6074,7 @@
         <v>1.44927536231884</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>2.5</v>
@@ -6072,10 +6083,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>10</v>
@@ -6118,7 +6129,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>51</v>
@@ -6127,13 +6138,13 @@
         <v>52</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0.9</v>
@@ -6143,7 +6154,7 @@
         <v>1.44927536231884</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J31" s="27" t="n">
         <v>2.5</v>
@@ -6152,10 +6163,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>10</v>
@@ -6198,7 +6209,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>53</v>
@@ -6207,13 +6218,13 @@
         <v>54</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.9</v>
@@ -6223,7 +6234,7 @@
         <v>6.76328502415459</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>2.5</v>
@@ -6232,10 +6243,10 @@
         <v>28</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>10</v>
@@ -6278,7 +6289,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>55</v>
@@ -6287,13 +6298,13 @@
         <v>56</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E33" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0.9</v>
@@ -6303,7 +6314,7 @@
         <v>2.89855072463768</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>2.5</v>
@@ -6312,10 +6323,10 @@
         <v>100</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>10</v>
@@ -6358,7 +6369,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>57</v>
@@ -6367,13 +6378,13 @@
         <v>58</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0.9</v>
@@ -6383,7 +6394,7 @@
         <v>2.89855072463768</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>2.5</v>
@@ -6392,10 +6403,10 @@
         <v>100</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>10</v>
@@ -6438,7 +6449,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>59</v>
@@ -6447,13 +6458,13 @@
         <v>60</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E35" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0.9</v>
@@ -6463,7 +6474,7 @@
         <v>2.89855072463768</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>2.5</v>
@@ -6472,10 +6483,10 @@
         <v>100</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>10</v>
@@ -6518,7 +6529,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>61</v>
@@ -6527,13 +6538,13 @@
         <v>62</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0.95</v>
@@ -6543,7 +6554,7 @@
         <v>2.2883295194508</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>2.5</v>
@@ -6552,10 +6563,10 @@
         <v>35</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>10</v>
@@ -6598,7 +6609,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>63</v>
@@ -6607,13 +6618,13 @@
         <v>64</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E37" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0.95</v>
@@ -6623,7 +6634,7 @@
         <v>1.37299771167048</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J37" s="27" t="n">
         <v>2.5</v>
@@ -6632,10 +6643,10 @@
         <v>35</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>10</v>
@@ -6678,12 +6689,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -6713,7 +6724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -6726,7 +6737,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6739,24 +6750,24 @@
         <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -6766,670 +6777,670 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>188</v>
-      </c>
       <c r="F7" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C8" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F8" s="22" t="s">
         <v>195</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C14" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C15" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C16" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C17" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C18" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C21" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C23" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C24" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C27" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C31" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C32" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C33" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C34" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C35" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C36" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>33</v>
+        <v>282</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C37" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>281</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>282</v>
+        <v>33</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C38" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>3</v>
@@ -7438,321 +7449,321 @@
         <v>286</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C40" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>53</v>
+        <v>293</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C41" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>291</v>
+        <v>53</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C42" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C43" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C44" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>297</v>
-      </c>
       <c r="E44" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C45" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>301</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>301</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C47" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B48" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="C48" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F48" s="22" t="s">
         <v>309</v>
-      </c>
-      <c r="C48" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C50" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C51" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C52" s="22" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
+      <c r="A53" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="C53" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C54" s="22" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>327</v>
+        <v>191</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="C55" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="F55" s="22" t="s">
+      <c r="A55" s="14" t="s">
         <v>331</v>
       </c>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="28" t="s">
@@ -7768,335 +7779,335 @@
         <v>334</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E57" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="B57" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="C57" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>327</v>
-      </c>
       <c r="F57" s="22" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C58" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C59" s="22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C60" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C61" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C62" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C63" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F64" s="22" t="s">
         <v>356</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="C64" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C65" s="22" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C66" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C67" s="22" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="28" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C68" s="22" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="28" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C69" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="28" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C70" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="28" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C71" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="28" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C72" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="28" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>379</v>
@@ -8105,179 +8116,219 @@
         <v>1</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="C74" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F74" s="22" t="s">
         <v>381</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="C74" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="F74" s="22" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="28" t="s">
-        <v>153</v>
+        <v>386</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C75" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>338</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="28" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C76" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="28" t="s">
-        <v>387</v>
+        <v>155</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C77" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="28" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C78" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="28" t="s">
-        <v>169</v>
+        <v>395</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C79" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="28" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C80" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
-        <v>394</v>
+        <v>171</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C81" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C82" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F82" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C83" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="E81" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="F81" s="22" t="s">
-        <v>338</v>
+      <c r="D83" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F83" s="22" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A55:F55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8310,7 +8361,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8320,7 +8371,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8332,36 +8383,36 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1</v>
@@ -8380,18 +8431,18 @@
         <v>17</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>10</v>
@@ -8410,18 +8461,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>10</v>
@@ -8440,18 +8491,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>10</v>
@@ -8470,18 +8521,18 @@
         <v>17</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>17</v>
@@ -8500,18 +8551,18 @@
         <v>18</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>17</v>
@@ -8530,18 +8581,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>16</v>
@@ -8560,18 +8611,18 @@
         <v>19</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>4</v>
@@ -8590,18 +8641,18 @@
         <v>19</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>3</v>
@@ -8620,18 +8671,18 @@
         <v>18</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>3</v>
@@ -8650,10 +8701,10 @@
         <v>17</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8677,7 +8728,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -8690,10 +8741,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>1</v>
@@ -8707,18 +8758,18 @@
         <v>19</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>1</v>
@@ -8732,18 +8783,18 @@
         <v>18</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>1</v>
@@ -8757,46 +8808,46 @@
         <v>17</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">ROUNDUP(('Kablo Çizelgesi'!K29+'Kablo Çizelgesi'!K30+'Kablo Çizelgesi'!K31)*(1+$C$3/100),0)</f>
         <v>220</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="22" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>67</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
@@ -8810,10 +8861,10 @@
         <v>67</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -8849,7 +8900,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8859,7 +8910,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8868,7 +8919,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="n">
@@ -8877,7 +8928,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="n">
@@ -8886,7 +8937,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="n">
@@ -8895,7 +8946,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="n">
@@ -8904,7 +8955,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="n">
@@ -8913,7 +8964,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="n">
@@ -8922,7 +8973,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="n">
@@ -8931,7 +8982,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="n">
@@ -8940,7 +8991,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="n">
@@ -8949,7 +9000,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="n">
@@ -8958,7 +9009,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="n">
@@ -8967,7 +9018,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="n">
@@ -8976,7 +9027,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="n">
@@ -8985,7 +9036,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="n">
@@ -8994,7 +9045,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="n">
@@ -9003,7 +9054,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="n">
@@ -9012,7 +9063,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="n">
@@ -9021,7 +9072,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
@@ -9030,7 +9081,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="n">
@@ -9039,7 +9090,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="n">
@@ -9048,7 +9099,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="n">
@@ -9057,7 +9108,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="n">
@@ -9069,498 +9120,498 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D28" s="33" t="n">
         <f aca="false">2*(($C$3+2*$C$5)+($C$4+2*$C$5))</f>
         <v>88</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D29" s="33" t="n">
         <f aca="false">ROUNDUP(D28*(1+$C$10/100),0)</f>
         <v>97</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D30" s="33" t="n">
         <f aca="false">2*(ROUNDUP(($C$3+2*$C$5)/$C$8,0)+ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>12</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D31" s="33" t="n">
         <f aca="false">D30*$C$7</f>
         <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">MAX(($C$3+2*$C$5)/ROUNDUP(($C$3+2*$C$5)/$C$8,0),($C$4+2*$C$5)/ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>7.33333333333333</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>473</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>465</v>
       </c>
       <c r="D33" s="33" t="n">
         <f aca="false">$C$15</f>
         <v>4</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D34" s="33" t="n">
         <f aca="false">MIN(8,MAX(2,ROUNDUP(2*($C$3+$C$4)/$C$9,0)))</f>
         <v>6</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D35" s="33" t="n">
         <f aca="false">D34</f>
         <v>6</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D36" s="33" t="n">
         <f aca="false">ROUNDUP((D34*($C$11+$C$6)+($C$13-$C$11)+(PI()*$C$14/2+2))*(1+$C$10/100),0)</f>
         <v>101</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D37" s="33" t="n">
         <f aca="false">ROUNDUP((2*($C$3+$C$4)+$C$4/2+3)*(1+$C$10/100),0)</f>
         <v>103</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D38" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">$C$23+$C$24+$C$25</f>
         <v>4.5</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="F39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D40" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D41" s="33" t="n">
         <f aca="false">ROUNDUP($C$16*(1+$C$10/100),0)</f>
         <v>3</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D42" s="33" t="n">
         <f aca="false">ROUNDUP($C$17*(1+$C$10/100),0)</f>
         <v>4</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D43" s="33" t="n">
         <f aca="false">ROUNDUP($C$22*(1+$C$10/100),0)</f>
         <v>33</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D44" s="33" t="n">
         <f aca="false">$C$18</f>
         <v>3</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D45" s="33" t="n">
         <f aca="false">($C$18-1)*$C$19+6</f>
         <v>18</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D46" s="33" t="n">
         <f aca="false">ROUNDUP($C$21*$C$20*(1+$C$10/100),0)</f>
         <v>80</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D48" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
         <v>27</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D50" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9568,17 +9619,17 @@
         <v>67</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D51" s="33" t="n">
         <f aca="false">ROUNDUP(D49/10,0)</f>
         <v>3</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -9623,7 +9674,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -9640,7 +9691,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9650,7 +9701,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9670,7 +9721,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9680,7 +9731,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9690,7 +9741,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -9700,7 +9751,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -9710,7 +9761,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -9720,7 +9771,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9730,7 +9781,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -9750,7 +9801,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9760,7 +9811,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -9770,7 +9821,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -9780,7 +9831,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -9790,7 +9841,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -9800,7 +9851,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -9810,7 +9861,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -9820,7 +9871,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -9830,7 +9881,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -9844,7 +9895,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -9853,12 +9904,12 @@
         <v>360.843918243516</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -9867,12 +9918,12 @@
         <v>9.0210979560879</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -9881,12 +9932,12 @@
         <v>0.0256</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -9895,12 +9946,12 @@
         <v>0.00832</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -9909,12 +9960,12 @@
         <v>0.0242102788088035</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -9923,12 +9974,12 @@
         <v>0.0056390977443609</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -9937,12 +9988,12 @@
         <v>0.0024</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -9951,12 +10002,12 @@
         <v>0.0300493485473292</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -9965,12 +10016,12 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -9984,45 +10035,45 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">$D$12</f>
@@ -10048,18 +10099,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>67</v>
@@ -10085,18 +10136,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>63</v>
@@ -10120,18 +10171,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>25</v>
@@ -10155,18 +10206,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="D39" s="22" t="n">
         <v>25</v>
@@ -10189,18 +10240,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>63</v>
@@ -10223,18 +10274,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>14</v>
@@ -10261,16 +10312,16 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="E42" s="22" t="n">
         <v>30</v>
@@ -10290,271 +10341,378 @@
         <v>UYGUN</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <f aca="false">$D$10</f>
-        <v>36</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <f aca="false">$D$20</f>
+      <c r="A43" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="D43" s="22" t="n">
         <v>25</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <f aca="false">$D$31</f>
+        <v>7.68536154160241</v>
       </c>
       <c r="I43" s="24" t="str">
         <f aca="false">IF(G43&gt;=H43,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
+      <c r="J43" s="13" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" s="22" t="n">
+        <f aca="false">$D$19</f>
+        <v>10</v>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <f aca="false">$D$31</f>
+        <v>7.68536154160241</v>
+      </c>
+      <c r="I44" s="24" t="str">
+        <f aca="false">IF(G44&gt;=H44,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-    </row>
-    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>607</v>
+      <c r="B45" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <f aca="false">$D$10</f>
+        <v>36</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <f aca="false">$D$20</f>
+        <v>25</v>
+      </c>
+      <c r="I45" s="24" t="str">
+        <f aca="false">IF(G45&gt;=H45,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="C47" s="8" t="n">
+      <c r="A47" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="C49" s="8" t="n">
         <f aca="false">$D$15</f>
         <v>1000</v>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D49" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="E47" s="12" t="n">
-        <f aca="false">C47/D47</f>
+      <c r="E49" s="12" t="n">
+        <f aca="false">C49/D49</f>
         <v>3.33333333333333</v>
       </c>
-      <c r="F47" s="22" t="str">
-        <f aca="false">IF(E47&gt;=$D$17,"UYGUN","UYGUN DEĞİL")</f>
+      <c r="F49" s="22" t="str">
+        <f aca="false">IF(E49&gt;=$D$17,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
-      <c r="G47" s="8" t="n">
+      <c r="G49" s="8" t="n">
         <f aca="false">$D$16</f>
         <v>300</v>
       </c>
-      <c r="H47" s="8" t="n">
+      <c r="H49" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="I47" s="22" t="str">
-        <f aca="false">IF(G47&gt;=H47+$D$18,"UYGUN","UYGUN DEĞİL")</f>
+      <c r="I49" s="22" t="str">
+        <f aca="false">IF(G49&gt;=H49+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
-      <c r="J47" s="24" t="str">
-        <f aca="false">IF(AND(F47="UYGUN",I47="UYGUN"),"SEÇİCİ","SEÇİCİ DEĞİL")</f>
+      <c r="J49" s="24" t="str">
+        <f aca="false">IF(AND(F49="UYGUN",I49="UYGUN"),"SEÇİCİ","SEÇİCİ DEĞİL")</f>
         <v>SEÇİCİ</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="C48" s="8" t="n">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>622</v>
+      </c>
+      <c r="C50" s="8" t="n">
         <f aca="false">$D$15</f>
         <v>1000</v>
       </c>
-      <c r="D48" s="8" t="n">
+      <c r="D50" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E48" s="12" t="n">
-        <f aca="false">C48/D48</f>
+      <c r="E50" s="12" t="n">
+        <f aca="false">C50/D50</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="F48" s="22" t="str">
-        <f aca="false">IF(E48&gt;=$D$17,"UYGUN","UYGUN DEĞİL")</f>
+      <c r="F50" s="22" t="str">
+        <f aca="false">IF(E50&gt;=$D$17,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
-      <c r="G48" s="8" t="n">
+      <c r="G50" s="8" t="n">
         <f aca="false">$D$16</f>
         <v>300</v>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H50" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="I48" s="22" t="str">
-        <f aca="false">IF(G48&gt;=H48+$D$18,"UYGUN","UYGUN DEĞİL")</f>
+      <c r="I50" s="22" t="str">
+        <f aca="false">IF(G50&gt;=H50+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
-      <c r="J48" s="24" t="str">
-        <f aca="false">IF(AND(F48="UYGUN",I48="UYGUN"),"SEÇİCİ","SEÇİCİ DEĞİL")</f>
+      <c r="J50" s="24" t="str">
+        <f aca="false">IF(AND(F50="UYGUN",I50="UYGUN"),"SEÇİCİ","SEÇİCİ DEĞİL")</f>
         <v>SEÇİCİ</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-    </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="18" t="n">
-        <f aca="false">$D$12*$D$13</f>
-        <v>960</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>615</v>
+      <c r="A51" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <f aca="false">$D$15</f>
+        <v>1000</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <f aca="false">C51/D51</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="F51" s="22" t="str">
+        <f aca="false">IF(E51&gt;=$D$17,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <f aca="false">$D$16</f>
+        <v>300</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I51" s="22" t="str">
+        <f aca="false">IF(G51&gt;=H51+$D$18,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="J51" s="24" t="str">
+        <f aca="false">IF(AND(F51="UYGUN",I51="UYGUN"),"SEÇİCİ","SEÇİCİ DEĞİL")</f>
+        <v>SEÇİCİ</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="18" t="n">
-        <f aca="false">$D$14</f>
-        <v>100</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="F53" s="24" t="str">
-        <f aca="false">IF(D53&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>618</v>
-      </c>
+      <c r="A53" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="18" t="n">
-        <f aca="false">$D$11</f>
-        <v>10</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="F54" s="24" t="str">
-        <f aca="false">IF(D54&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
-      </c>
-      <c r="J54" s="13" t="s">
-        <v>620</v>
+      <c r="A54" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="18" t="n">
+        <f aca="false">$D$12*$D$13</f>
+        <v>960</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="18" t="n">
+        <f aca="false">$D$14</f>
+        <v>100</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="F56" s="24" t="str">
+        <f aca="false">IF(D56&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="18" t="n">
+        <f aca="false">$D$11</f>
+        <v>10</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="F57" s="24" t="str">
+        <f aca="false">IF(D57&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="18" t="n">
         <f aca="false">$D$31</f>
         <v>7.68536154160241</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="25" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="25" t="s">
-        <v>624</v>
+      <c r="E58" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="25" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="25" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -10588,12 +10746,12 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A53:J53"/>
     <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>1.15942028985507</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>162</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>163</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>191</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>195</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7552,7 +7552,7 @@
         <v>191</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>195</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8302,7 +8302,7 @@
         <v>335</v>
       </c>
       <c r="F82" s="22" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="651">
   <si>
     <t xml:space="preserve">YÜK DENGESİ VE FAZ DENGESİZLİĞİ</t>
   </si>
@@ -1171,6 +1171,27 @@
     <t xml:space="preserve">100 W, hat PJ3</t>
   </si>
   <si>
+    <t xml:space="preserve">HP1–HP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoparlör (ses kolu, hat gerilimli/doğrudan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W, hat SS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP5–HP8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W, hat SS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP9–HP12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W, hat SS3</t>
+  </si>
+  <si>
     <t xml:space="preserve">JB1</t>
   </si>
   <si>
@@ -1316,6 +1337,21 @@
   </si>
   <si>
     <t xml:space="preserve">W16: NYY 3x2,5 mm², L=67 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoparlör (ses kolu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W18: NYY 3x2,5 mm², L=100 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kol gücü hoparlörlere eşit bölünmüştür (varsayım)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W19: NYY 3x2,5 mm², L=100 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20: NYY 3x2,5 mm², L=100 m</t>
   </si>
   <si>
     <t xml:space="preserve">EK KALEMLER</t>
@@ -3181,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
@@ -3229,7 +3265,7 @@
         <v>1.15942028985507</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
@@ -5647,7 +5683,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>162</v>
       </c>
@@ -5727,7 +5763,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>163</v>
       </c>
@@ -6724,7 +6760,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -8093,7 +8129,7 @@
         <v>379</v>
       </c>
       <c r="C72" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>380</v>
@@ -8102,67 +8138,67 @@
         <v>335</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="28" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>379</v>
       </c>
       <c r="C73" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E73" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>379</v>
       </c>
       <c r="C74" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="B75" s="13" t="s">
         <v>386</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>387</v>
       </c>
       <c r="C75" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E75" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8170,27 +8206,27 @@
         <v>389</v>
       </c>
       <c r="B76" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C76" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>390</v>
-      </c>
-      <c r="C76" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>391</v>
       </c>
       <c r="E76" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="28" t="s">
-        <v>155</v>
+        <v>391</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C77" s="22" t="n">
         <v>1</v>
@@ -8202,7 +8238,7 @@
         <v>335</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8210,33 +8246,33 @@
         <v>393</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C78" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E78" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="28" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C79" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E79" s="22" t="s">
         <v>335</v>
@@ -8247,16 +8283,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="B80" s="13" t="s">
-        <v>390</v>
-      </c>
       <c r="C80" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E80" s="22" t="s">
         <v>335</v>
@@ -8267,16 +8303,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
-        <v>171</v>
+        <v>400</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C81" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>335</v>
@@ -8287,41 +8323,101 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="28" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C82" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F82" s="22" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="28" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C83" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E83" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F83" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C84" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="E84" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F84" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C85" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F85" s="22" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="C86" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="E86" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F86" s="22" t="s">
         <v>346</v>
       </c>
     </row>
@@ -8345,7 +8441,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -8361,7 +8457,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8371,7 +8467,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8383,28 +8479,28 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>183</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8431,10 +8527,10 @@
         <v>17</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8442,7 +8538,7 @@
         <v>357</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>10</v>
@@ -8461,10 +8557,10 @@
         <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8472,7 +8568,7 @@
         <v>360</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>10</v>
@@ -8491,10 +8587,10 @@
         <v>19</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8502,7 +8598,7 @@
         <v>362</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>10</v>
@@ -8521,10 +8617,10 @@
         <v>17</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8551,10 +8647,10 @@
         <v>18</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8581,10 +8677,10 @@
         <v>17</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8611,10 +8707,10 @@
         <v>19</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8641,10 +8737,10 @@
         <v>19</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8671,10 +8767,10 @@
         <v>18</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8701,176 +8797,266 @@
         <v>17</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <f aca="false">C16*D16</f>
+        <v>600</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <f aca="false">C17*D17</f>
+        <v>600</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <f aca="false">C18*D18</f>
+        <v>600</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="32" t="n">
-        <f aca="false">SUM(C6:C15)</f>
-        <v>91</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="32" t="n">
-        <f aca="false">SUM(E6:E15)</f>
-        <v>12750</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>428</v>
-      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="32" t="n">
+        <f aca="false">SUM(C6:C18)</f>
+        <v>103</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="32" t="n">
+        <f aca="false">SUM(E6:E18)</f>
+        <v>14550</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>428</v>
-      </c>
+      <c r="A21" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="C22" s="33" t="n">
+        <v>386</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C25" s="33" t="n">
         <f aca="false">ROUNDUP(('Kablo Çizelgesi'!K29+'Kablo Çizelgesi'!K30+'Kablo Çizelgesi'!K31)*(1+$C$3/100),0)</f>
         <v>220</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="22" t="s">
-        <v>431</v>
-      </c>
-      <c r="G22" s="22" t="s">
+      <c r="D25" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="G25" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="C23" s="10" t="n">
+      <c r="H25" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22" t="s">
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G26" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>436</v>
+      <c r="H26" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8900,7 +9086,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8910,7 +9096,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8919,7 +9105,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="n">
@@ -8928,7 +9114,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="n">
@@ -8937,7 +9123,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="n">
@@ -8946,7 +9132,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="n">
@@ -8955,7 +9141,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="n">
@@ -8964,7 +9150,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="n">
@@ -8973,7 +9159,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="n">
@@ -8982,7 +9168,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="n">
@@ -8991,7 +9177,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="n">
@@ -9000,7 +9186,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="n">
@@ -9009,7 +9195,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="n">
@@ -9018,7 +9204,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="n">
@@ -9027,7 +9213,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="n">
@@ -9036,7 +9222,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="n">
@@ -9045,7 +9231,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="n">
@@ -9054,7 +9240,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="n">
@@ -9063,7 +9249,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="n">
@@ -9072,7 +9258,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
@@ -9081,7 +9267,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="n">
@@ -9090,7 +9276,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="n">
@@ -9099,7 +9285,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="n">
@@ -9108,7 +9294,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="n">
@@ -9120,16 +9306,16 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>184</v>
@@ -9137,313 +9323,313 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D28" s="33" t="n">
         <f aca="false">2*(($C$3+2*$C$5)+($C$4+2*$C$5))</f>
         <v>88</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D29" s="33" t="n">
         <f aca="false">ROUNDUP(D28*(1+$C$10/100),0)</f>
         <v>97</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D30" s="33" t="n">
         <f aca="false">2*(ROUNDUP(($C$3+2*$C$5)/$C$8,0)+ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>12</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D31" s="33" t="n">
         <f aca="false">D30*$C$7</f>
         <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">MAX(($C$3+2*$C$5)/ROUNDUP(($C$3+2*$C$5)/$C$8,0),($C$4+2*$C$5)/ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>7.33333333333333</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D33" s="33" t="n">
         <f aca="false">$C$15</f>
         <v>4</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="C34" s="22" t="s">
         <v>485</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>473</v>
       </c>
       <c r="D34" s="33" t="n">
         <f aca="false">MIN(8,MAX(2,ROUNDUP(2*($C$3+$C$4)/$C$9,0)))</f>
         <v>6</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D35" s="33" t="n">
         <f aca="false">D34</f>
         <v>6</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D36" s="33" t="n">
         <f aca="false">ROUNDUP((D34*($C$11+$C$6)+($C$13-$C$11)+(PI()*$C$14/2+2))*(1+$C$10/100),0)</f>
         <v>101</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D37" s="33" t="n">
         <f aca="false">ROUNDUP((2*($C$3+$C$4)+$C$4/2+3)*(1+$C$10/100),0)</f>
         <v>103</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D38" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">$C$23+$C$24+$C$25</f>
         <v>4.5</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D40" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D41" s="33" t="n">
         <f aca="false">ROUNDUP($C$16*(1+$C$10/100),0)</f>
         <v>3</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D42" s="33" t="n">
         <f aca="false">ROUNDUP($C$17*(1+$C$10/100),0)</f>
         <v>4</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9451,167 +9637,167 @@
         <v>340</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D43" s="33" t="n">
         <f aca="false">ROUNDUP($C$22*(1+$C$10/100),0)</f>
         <v>33</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D44" s="33" t="n">
         <f aca="false">$C$18</f>
         <v>3</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D45" s="33" t="n">
         <f aca="false">($C$18-1)*$C$19+6</f>
         <v>18</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D46" s="33" t="n">
         <f aca="false">ROUNDUP($C$21*$C$20*(1+$C$10/100),0)</f>
         <v>80</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D48" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
         <v>27</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D50" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9619,17 +9805,17 @@
         <v>67</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D51" s="33" t="n">
         <f aca="false">ROUNDUP(D49/10,0)</f>
         <v>3</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -9691,7 +9877,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9701,7 +9887,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9721,7 +9907,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9731,7 +9917,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9741,7 +9927,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -9751,7 +9937,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -9771,7 +9957,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9781,7 +9967,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -9801,7 +9987,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9811,7 +9997,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -9821,7 +10007,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -9831,7 +10017,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -9841,7 +10027,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -9851,7 +10037,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -9861,7 +10047,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -9871,7 +10057,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -9881,7 +10067,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -9895,7 +10081,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -9904,12 +10090,12 @@
         <v>360.843918243516</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -9918,12 +10104,12 @@
         <v>9.0210979560879</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -9932,12 +10118,12 @@
         <v>0.0256</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -9946,12 +10132,12 @@
         <v>0.00832</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -9960,12 +10146,12 @@
         <v>0.0242102788088035</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -9974,12 +10160,12 @@
         <v>0.0056390977443609</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -9988,12 +10174,12 @@
         <v>0.0024</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -10002,12 +10188,12 @@
         <v>0.0300493485473292</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -10016,12 +10202,12 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -10035,45 +10221,45 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="B35" s="28" t="s">
         <v>141</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">$D$12</f>
@@ -10099,18 +10285,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>199</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>67</v>
@@ -10136,18 +10322,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>273</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>63</v>
@@ -10171,18 +10357,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>240</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>25</v>
@@ -10206,18 +10392,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="D39" s="22" t="n">
         <v>25</v>
@@ -10240,18 +10426,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>63</v>
@@ -10274,18 +10460,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="B41" s="28" t="s">
         <v>279</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>14</v>
@@ -10312,16 +10498,16 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="E42" s="22" t="n">
         <v>30</v>
@@ -10341,18 +10527,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="B43" s="28" t="s">
         <v>282</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="D43" s="22" t="n">
         <v>25</v>
@@ -10375,18 +10561,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>297</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>10</v>
@@ -10410,15 +10596,15 @@
         <v>UYGUN</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="G45" s="8" t="n">
         <f aca="false">$D$10</f>
@@ -10435,7 +10621,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -10449,34 +10635,34 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10484,7 +10670,7 @@
         <v>199</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C49" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10522,7 +10708,7 @@
         <v>199</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C50" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10560,7 +10746,7 @@
         <v>199</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C51" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10595,7 +10781,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -10609,29 +10795,29 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -10640,15 +10826,15 @@
         <v>960</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -10657,19 +10843,19 @@
         <v>100</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="F56" s="24" t="str">
         <f aca="false">IF(D56&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -10678,19 +10864,19 @@
         <v>10</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="F57" s="24" t="str">
         <f aca="false">IF(D57&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -10699,20 +10885,20 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="654">
   <si>
     <t xml:space="preserve">YÜK DENGESİ VE FAZ DENGESİZLİĞİ</t>
   </si>
@@ -1078,6 +1078,18 @@
     <t xml:space="preserve">Ç1</t>
   </si>
   <si>
+    <t xml:space="preserve">AMF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses amfisi (çok bölgeli, raf tipi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,8 kW toplam ses hattı gücü; elektrik odasında PN1 yanı (yer varsayımı)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ç6</t>
+  </si>
+  <si>
     <t xml:space="preserve">UPS1</t>
   </si>
   <si>
@@ -1199,9 +1211,6 @@
   </si>
   <si>
     <t xml:space="preserve">hat PJ1, IP65, 3x2,5 mm² geçişli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ç6</t>
   </si>
   <si>
     <t xml:space="preserve">JB2</t>
@@ -6760,7 +6769,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -7898,21 +7907,21 @@
         <v>335</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C61" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E61" s="22" t="s">
         <v>335</v>
@@ -7921,24 +7930,24 @@
         <v>346</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="28" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C62" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E62" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7949,7 +7958,7 @@
         <v>358</v>
       </c>
       <c r="C63" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>359</v>
@@ -7958,247 +7967,247 @@
         <v>335</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C64" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E64" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>362</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>358</v>
       </c>
       <c r="C65" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E65" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C66" s="22" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E66" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C67" s="22" t="n">
         <v>17</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E67" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="B68" s="13" t="s">
-        <v>365</v>
-      </c>
       <c r="C68" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E68" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="28" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C69" s="22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E69" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="28" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C70" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E70" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>376</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>372</v>
       </c>
       <c r="C71" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E71" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="28" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C72" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E72" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="28" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C73" s="22" t="n">
         <v>4</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E73" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="B74" s="13" t="s">
         <v>383</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>379</v>
       </c>
       <c r="C74" s="22" t="n">
         <v>4</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="28" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C75" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E75" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8206,47 +8215,47 @@
         <v>389</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C76" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E76" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>388</v>
+        <v>350</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C77" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E77" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>388</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="28" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C78" s="22" t="n">
         <v>1</v>
@@ -8258,7 +8267,7 @@
         <v>335</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>388</v>
+        <v>350</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8269,7 +8278,7 @@
         <v>397</v>
       </c>
       <c r="C79" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>398</v>
@@ -8278,21 +8287,21 @@
         <v>335</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="28" t="s">
-        <v>155</v>
+        <v>399</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C80" s="22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E80" s="22" t="s">
         <v>335</v>
@@ -8303,16 +8312,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B81" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="B81" s="13" t="s">
-        <v>397</v>
-      </c>
       <c r="C81" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>335</v>
@@ -8323,16 +8332,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="28" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C82" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>335</v>
@@ -8343,16 +8352,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="28" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C83" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E83" s="22" t="s">
         <v>335</v>
@@ -8363,16 +8372,16 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="28" t="s">
-        <v>171</v>
+        <v>407</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C84" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E84" s="22" t="s">
         <v>335</v>
@@ -8383,41 +8392,61 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="28" t="s">
-        <v>407</v>
+        <v>171</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C85" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E85" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F85" s="22" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="28" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C86" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E86" s="22" t="s">
         <v>335</v>
       </c>
       <c r="F86" s="22" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="C87" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="F87" s="22" t="s">
         <v>346</v>
       </c>
     </row>
@@ -8457,7 +8486,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8467,7 +8496,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8479,36 +8508,36 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>183</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1</v>
@@ -8527,18 +8556,18 @@
         <v>17</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>10</v>
@@ -8557,18 +8586,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>10</v>
@@ -8587,18 +8616,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>10</v>
@@ -8617,18 +8646,18 @@
         <v>17</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>17</v>
@@ -8647,18 +8676,18 @@
         <v>18</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>17</v>
@@ -8677,18 +8706,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>369</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>365</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>16</v>
@@ -8707,18 +8736,18 @@
         <v>19</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>4</v>
@@ -8737,18 +8766,18 @@
         <v>19</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>3</v>
@@ -8767,18 +8796,18 @@
         <v>18</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>376</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>372</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>3</v>
@@ -8797,18 +8826,18 @@
         <v>17</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>4</v>
@@ -8827,18 +8856,18 @@
         <v>19</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>4</v>
@@ -8857,18 +8886,18 @@
         <v>19</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>4</v>
@@ -8887,10 +8916,10 @@
         <v>19</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8914,7 +8943,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -8927,10 +8956,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>1</v>
@@ -8947,15 +8976,15 @@
         <v>168</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
@@ -8972,15 +9001,15 @@
         <v>169</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>1</v>
@@ -8997,43 +9026,43 @@
         <v>170</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C25" s="33" t="n">
         <f aca="false">ROUNDUP(('Kablo Çizelgesi'!K29+'Kablo Çizelgesi'!K30+'Kablo Çizelgesi'!K31)*(1+$C$3/100),0)</f>
         <v>220</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="22" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>67</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>1</v>
@@ -9047,10 +9076,10 @@
         <v>67</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -9086,7 +9115,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9096,7 +9125,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -9105,7 +9134,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="n">
@@ -9114,7 +9143,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="n">
@@ -9123,7 +9152,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="n">
@@ -9132,7 +9161,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="n">
@@ -9141,7 +9170,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="n">
@@ -9150,7 +9179,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="n">
@@ -9159,7 +9188,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="n">
@@ -9168,7 +9197,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="n">
@@ -9177,7 +9206,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="n">
@@ -9186,7 +9215,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="n">
@@ -9195,7 +9224,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="n">
@@ -9204,7 +9233,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="n">
@@ -9213,7 +9242,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="n">
@@ -9222,7 +9251,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="n">
@@ -9231,7 +9260,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="n">
@@ -9240,7 +9269,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="n">
@@ -9249,7 +9278,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="n">
@@ -9258,7 +9287,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
@@ -9267,7 +9296,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="n">
@@ -9276,7 +9305,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="n">
@@ -9285,7 +9314,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="n">
@@ -9294,7 +9323,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="n">
@@ -9306,16 +9335,16 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>184</v>
@@ -9323,313 +9352,313 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D28" s="33" t="n">
         <f aca="false">2*(($C$3+2*$C$5)+($C$4+2*$C$5))</f>
         <v>88</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D29" s="33" t="n">
         <f aca="false">ROUNDUP(D28*(1+$C$10/100),0)</f>
         <v>97</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D30" s="33" t="n">
         <f aca="false">2*(ROUNDUP(($C$3+2*$C$5)/$C$8,0)+ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>12</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D31" s="33" t="n">
         <f aca="false">D30*$C$7</f>
         <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">MAX(($C$3+2*$C$5)/ROUNDUP(($C$3+2*$C$5)/$C$8,0),($C$4+2*$C$5)/ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>7.33333333333333</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D33" s="33" t="n">
         <f aca="false">$C$15</f>
         <v>4</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D34" s="33" t="n">
         <f aca="false">MIN(8,MAX(2,ROUNDUP(2*($C$3+$C$4)/$C$9,0)))</f>
         <v>6</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D35" s="33" t="n">
         <f aca="false">D34</f>
         <v>6</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D36" s="33" t="n">
         <f aca="false">ROUNDUP((D34*($C$11+$C$6)+($C$13-$C$11)+(PI()*$C$14/2+2))*(1+$C$10/100),0)</f>
         <v>101</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D37" s="33" t="n">
         <f aca="false">ROUNDUP((2*($C$3+$C$4)+$C$4/2+3)*(1+$C$10/100),0)</f>
         <v>103</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D38" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">$C$23+$C$24+$C$25</f>
         <v>4.5</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D40" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D41" s="33" t="n">
         <f aca="false">ROUNDUP($C$16*(1+$C$10/100),0)</f>
         <v>3</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D42" s="33" t="n">
         <f aca="false">ROUNDUP($C$17*(1+$C$10/100),0)</f>
         <v>4</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9637,167 +9666,167 @@
         <v>340</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D43" s="33" t="n">
         <f aca="false">ROUNDUP($C$22*(1+$C$10/100),0)</f>
         <v>33</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D44" s="33" t="n">
         <f aca="false">$C$18</f>
         <v>3</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D45" s="33" t="n">
         <f aca="false">($C$18-1)*$C$19+6</f>
         <v>18</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D46" s="33" t="n">
         <f aca="false">ROUNDUP($C$21*$C$20*(1+$C$10/100),0)</f>
         <v>80</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D48" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
         <v>27</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D50" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9805,17 +9834,17 @@
         <v>67</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D51" s="33" t="n">
         <f aca="false">ROUNDUP(D49/10,0)</f>
         <v>3</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -9877,7 +9906,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9887,7 +9916,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9907,7 +9936,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9917,7 +9946,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9927,7 +9956,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -9937,7 +9966,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -9957,7 +9986,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9967,7 +9996,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -9987,7 +10016,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9997,7 +10026,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -10007,7 +10036,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -10017,7 +10046,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -10027,7 +10056,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -10037,7 +10066,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -10047,7 +10076,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10057,7 +10086,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -10067,7 +10096,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -10081,7 +10110,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -10090,12 +10119,12 @@
         <v>360.843918243516</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -10104,12 +10133,12 @@
         <v>9.0210979560879</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -10118,12 +10147,12 @@
         <v>0.0256</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -10132,12 +10161,12 @@
         <v>0.00832</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -10146,12 +10175,12 @@
         <v>0.0242102788088035</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -10160,12 +10189,12 @@
         <v>0.0056390977443609</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -10174,12 +10203,12 @@
         <v>0.0024</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -10188,12 +10217,12 @@
         <v>0.0300493485473292</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -10202,12 +10231,12 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -10221,45 +10250,45 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B35" s="28" t="s">
         <v>141</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">$D$12</f>
@@ -10285,18 +10314,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>199</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>67</v>
@@ -10322,18 +10351,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>273</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>63</v>
@@ -10357,18 +10386,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>240</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>25</v>
@@ -10392,18 +10421,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D39" s="22" t="n">
         <v>25</v>
@@ -10426,18 +10455,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>63</v>
@@ -10460,18 +10489,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B41" s="28" t="s">
         <v>279</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>14</v>
@@ -10498,16 +10527,16 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E42" s="22" t="n">
         <v>30</v>
@@ -10527,18 +10556,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B43" s="28" t="s">
         <v>282</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D43" s="22" t="n">
         <v>25</v>
@@ -10561,18 +10590,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>297</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>10</v>
@@ -10596,15 +10625,15 @@
         <v>UYGUN</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G45" s="8" t="n">
         <f aca="false">$D$10</f>
@@ -10621,7 +10650,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -10635,34 +10664,34 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10670,7 +10699,7 @@
         <v>199</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C49" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10708,7 +10737,7 @@
         <v>199</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C50" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10746,7 +10775,7 @@
         <v>199</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C51" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10781,7 +10810,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -10795,29 +10824,29 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -10826,15 +10855,15 @@
         <v>960</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -10843,19 +10872,19 @@
         <v>100</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F56" s="24" t="str">
         <f aca="false">IF(D56&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -10864,19 +10893,19 @@
         <v>10</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F57" s="24" t="str">
         <f aca="false">IF(D57&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -10885,20 +10914,20 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="661">
   <si>
     <t xml:space="preserve">YÜK DENGESİ VE FAZ DENGESİZLİĞİ</t>
   </si>
@@ -178,21 +178,21 @@
     <t xml:space="preserve">PJ1</t>
   </si>
   <si>
-    <t xml:space="preserve">Projektör hattı-1
+    <t xml:space="preserve">Projektör-1
 (PR1–PR4)</t>
   </si>
   <si>
     <t xml:space="preserve">PJ2</t>
   </si>
   <si>
-    <t xml:space="preserve">Projektör hattı-2
+    <t xml:space="preserve">Projektör-2
 (PR5–PR7)</t>
   </si>
   <si>
     <t xml:space="preserve">PJ3</t>
   </si>
   <si>
-    <t xml:space="preserve">Projektör hattı-3
+    <t xml:space="preserve">Projektör-3
 (PR8–PR10)</t>
   </si>
   <si>
@@ -202,6 +202,12 @@
     <t xml:space="preserve">Kamera / NVR (UPS1)</t>
   </si>
   <si>
+    <t xml:space="preserve">AM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses amfisi (AMF1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS1</t>
   </si>
   <si>
@@ -337,13 +343,13 @@
     <t xml:space="preserve">en az yüklü faz (SS2 aynı ortak RCD altında, aynı faz)</t>
   </si>
   <si>
-    <t xml:space="preserve">Projektör hattı-1 (PR1–PR4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projektör hattı-2 (PR5–PR7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projektör hattı-3 (PR8–PR10)</t>
+    <t xml:space="preserve">Projektör-1 (PR1–PR4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektör-2 (PR5–PR7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projektör-3 (PR8–PR10)</t>
   </si>
   <si>
     <t xml:space="preserve">İç LED hat-1 (L1–L17)</t>
@@ -556,22 +562,25 @@
     <t xml:space="preserve">W18</t>
   </si>
   <si>
+    <t xml:space="preserve">W19</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCB 1P+N C10 (RCD3 altında)</t>
   </si>
   <si>
-    <t xml:space="preserve">W19</t>
-  </si>
-  <si>
     <t xml:space="preserve">W20</t>
   </si>
   <si>
     <t xml:space="preserve">W21</t>
   </si>
   <si>
+    <t xml:space="preserve">W22</t>
+  </si>
+  <si>
     <t xml:space="preserve">NHXH FE180/E90 3x2,5 mm² Cu</t>
   </si>
   <si>
-    <t xml:space="preserve">W22</t>
+    <t xml:space="preserve">W23</t>
   </si>
   <si>
     <t xml:space="preserve">Kontroller: Ib ≤ In ≤ Iz(düzeltilmiş) ve toplam ΔU = ΔU hat + ΔU besleme ≤ limit. ΔU = (√3 veya 2)·I·L·(cosφ/(κ·S) + X·sinφ).</t>
@@ -928,6 +937,9 @@
     <t xml:space="preserve">Kamera hattı RCBO</t>
   </si>
   <si>
+    <t xml:space="preserve">Ses sistemi hattı RCBO</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS1, SS2</t>
   </si>
   <si>
@@ -937,9 +949,6 @@
     <t xml:space="preserve">1P+N C10 A, 10 kA</t>
   </si>
   <si>
-    <t xml:space="preserve">Ses sistemi hattı RCBO</t>
-  </si>
-  <si>
     <t xml:space="preserve">AC1, YA1</t>
   </si>
   <si>
@@ -1081,138 +1090,147 @@
     <t xml:space="preserve">AMF1</t>
   </si>
   <si>
-    <t xml:space="preserve">Ses amfisi (çok bölgeli, raf tipi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,8 kW toplam ses hattı gücü; elektrik odasında PN1 yanı (yer varsayımı)</t>
+    <t xml:space="preserve">Ses amfisi (3 çıkışlı, raf tipi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,3 kW besleme (AM1), elektrik odasında PN1 yanı (yer ve güç varsayımı)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ç1, Ç6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK1–SK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses hattı kablosu: amfi çıkışı → sağ hoparlör kolu (SS1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x1,5 mm² ekranlı (LiYCY), L=100,0 m (kol boyuyla aynı, varsayım)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPS, 2 kVA, online çift dönüşümlü (kamera/NVR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,0 kVA, 230 V, kamera/NVR için</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avize dimmer (LED uyumlu, faz kesmeli, 2,5 kW) / kontaktör</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avize hattı AV1 üzerinde, 2,5 kW LED uyumlu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Büyük avize + bağlantı ünitesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000 W, hat AV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1–P10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priz girişi, 16 A, 230 V, topraklı (IP20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 W, hat PZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P11–P20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 W, hat PZ2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P21–P30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 W, hat PZ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1–L17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İç mekan LED armatür/lamba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 W, hat LD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L18–L34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 W, hat LD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L35–L50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 W, hat LD3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR1–PR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED projektör, IP65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 W, hat PJ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR5–PR7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 W, hat PJ2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR8–PR10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 W, hat PJ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP1–HP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoparlör (ses kolu, hat gerilimli/doğrudan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W, hat SS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP5–HP8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W, hat SS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP9–HP12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W, hat SS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP65 bağlantı kutusu (dış hat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hat PJ1, IP65, 3x2,5 mm² geçişli</t>
   </si>
   <si>
     <t xml:space="preserve">Ç6</t>
   </si>
   <si>
-    <t xml:space="preserve">UPS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPS, 2 kVA, online çift dönüşümlü (kamera/NVR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,0 kVA, 230 V, kamera/NVR için</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avize dimmer (LED uyumlu, faz kesmeli, 2,5 kW) / kontaktör</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avize hattı AV1 üzerinde, 2,5 kW LED uyumlu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Büyük avize + bağlantı ünitesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000 W, hat AV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ç1, Ç6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1–P10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priz girişi, 16 A, 230 V, topraklı (IP20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 W, hat PZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P11–P20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 W, hat PZ2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P21–P30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 W, hat PZ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1–L17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İç mekan LED armatür/lamba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 W, hat LD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L18–L34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 W, hat LD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L35–L50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 W, hat LD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR1–PR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED projektör, IP65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 W, hat PJ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR5–PR7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 W, hat PJ2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR8–PR10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 W, hat PJ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP1–HP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hoparlör (ses kolu, hat gerilimli/doğrudan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 W, hat SS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP5–HP8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 W, hat SS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP9–HP12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 W, hat SS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IP65 bağlantı kutusu (dış hat)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hat PJ1, IP65, 3x2,5 mm² geçişli</t>
-  </si>
-  <si>
     <t xml:space="preserve">JB2</t>
   </si>
   <si>
@@ -1267,13 +1285,16 @@
     <t xml:space="preserve">NYY 3x2,5 mm² Cu, L=28,0 m</t>
   </si>
   <si>
-    <t xml:space="preserve">W18–W20</t>
+    <t xml:space="preserve">NYY 3x2,5 mm² Cu, L=5,0 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W19–W21</t>
   </si>
   <si>
     <t xml:space="preserve">NYY 3x2,5 mm² Cu, L=100,0 m</t>
   </si>
   <si>
-    <t xml:space="preserve">W21, W22</t>
+    <t xml:space="preserve">W22, W23</t>
   </si>
   <si>
     <t xml:space="preserve">NHXH FE180/E90 3x2,5 mm² Cu, L=35,0 m</t>
@@ -1351,18 +1372,18 @@
     <t xml:space="preserve">Hoparlör (ses kolu)</t>
   </si>
   <si>
-    <t xml:space="preserve">W18: NYY 3x2,5 mm², L=100 m</t>
+    <t xml:space="preserve">W19: NYY 3x2,5 mm², L=100 m</t>
   </si>
   <si>
     <t xml:space="preserve">kol gücü hoparlörlere eşit bölünmüştür (varsayım)</t>
   </si>
   <si>
-    <t xml:space="preserve">W19: NYY 3x2,5 mm², L=100 m</t>
-  </si>
-  <si>
     <t xml:space="preserve">W20: NYY 3x2,5 mm², L=100 m</t>
   </si>
   <si>
+    <t xml:space="preserve">W21: NYY 3x2,5 mm², L=100 m</t>
+  </si>
+  <si>
     <t xml:space="preserve">EK KALEMLER</t>
   </si>
   <si>
@@ -1879,7 +1900,7 @@
     <t xml:space="preserve">MPCB 3P 11-16 A</t>
   </si>
   <si>
-    <t xml:space="preserve">AV1, PZ1–PZ3, LD1–LD3, PJ1–PJ3, KR1, SS3, AC1, YA1</t>
+    <t xml:space="preserve">AV1, PZ1–PZ3, LD1–LD3, PJ1–PJ3, KR1, AM1, SS3, AC1, YA1</t>
   </si>
   <si>
     <t xml:space="preserve">RCBO 1P+N, 30 mA, Tip A</t>
@@ -2538,7 +2559,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -3141,7 +3162,7 @@
         <v>0.255</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>0.9</v>
@@ -3155,11 +3176,11 @@
       </c>
       <c r="H20" s="11" t="n">
         <f aca="false">IF($D20="3F",$G20/3,IF($D20=H$9,$G20,0))</f>
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="I20" s="11" t="n">
         <f aca="false">IF($D20="3F",$G20/3,IF($D20=I$9,$G20,0))</f>
-        <v>0.255</v>
+        <v>0</v>
       </c>
       <c r="J20" s="11" t="n">
         <f aca="false">IF($D20="3F",$G20/3,IF($D20=J$9,$G20,0))</f>
@@ -3167,11 +3188,11 @@
       </c>
       <c r="K20" s="12" t="n">
         <f aca="false">IF($D20="3F",$G20*1000/(3*$B$4*$E20),IF($D20=K$9,$G20*1000/($B$4*$E20),0))</f>
-        <v>0</v>
+        <v>1.23188405797101</v>
       </c>
       <c r="L20" s="12" t="n">
         <f aca="false">IF($D20="3F",$G20*1000/(3*$B$4*$E20),IF($D20=L$9,$G20*1000/($B$4*$E20),0))</f>
-        <v>1.23188405797101</v>
+        <v>0</v>
       </c>
       <c r="M20" s="12" t="n">
         <f aca="false">IF($D20="3F",$G20*1000/(3*$B$4*$E20),IF($D20=M$9,$G20*1000/($B$4*$E20),0))</f>
@@ -3189,7 +3210,7 @@
         <v>0.255</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>0.9</v>
@@ -3203,7 +3224,7 @@
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">IF($D21="3F",$G21/3,IF($D21=H$9,$G21,0))</f>
-        <v>0.255</v>
+        <v>0</v>
       </c>
       <c r="I21" s="11" t="n">
         <f aca="false">IF($D21="3F",$G21/3,IF($D21=I$9,$G21,0))</f>
@@ -3211,11 +3232,11 @@
       </c>
       <c r="J21" s="11" t="n">
         <f aca="false">IF($D21="3F",$G21/3,IF($D21=J$9,$G21,0))</f>
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="K21" s="12" t="n">
         <f aca="false">IF($D21="3F",$G21*1000/(3*$B$4*$E21),IF($D21=K$9,$G21*1000/($B$4*$E21),0))</f>
-        <v>1.23188405797101</v>
+        <v>0</v>
       </c>
       <c r="L21" s="12" t="n">
         <f aca="false">IF($D21="3F",$G21*1000/(3*$B$4*$E21),IF($D21=L$9,$G21*1000/($B$4*$E21),0))</f>
@@ -3223,7 +3244,7 @@
       </c>
       <c r="M21" s="12" t="n">
         <f aca="false">IF($D21="3F",$G21*1000/(3*$B$4*$E21),IF($D21=M$9,$G21*1000/($B$4*$E21),0))</f>
-        <v>0</v>
+        <v>1.23188405797101</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3237,7 +3258,7 @@
         <v>0.24</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>0.9</v>
@@ -3255,11 +3276,11 @@
       </c>
       <c r="I22" s="11" t="n">
         <f aca="false">IF($D22="3F",$G22/3,IF($D22=I$9,$G22,0))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">IF($D22="3F",$G22/3,IF($D22=J$9,$G22,0))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <f aca="false">IF($D22="3F",$G22*1000/(3*$B$4*$E22),IF($D22=K$9,$G22*1000/($B$4*$E22),0))</f>
@@ -3267,11 +3288,11 @@
       </c>
       <c r="L22" s="12" t="n">
         <f aca="false">IF($D22="3F",$G22*1000/(3*$B$4*$E22),IF($D22=L$9,$G22*1000/($B$4*$E22),0))</f>
-        <v>0</v>
+        <v>1.15942028985507</v>
       </c>
       <c r="M22" s="12" t="n">
         <f aca="false">IF($D22="3F",$G22*1000/(3*$B$4*$E22),IF($D22=M$9,$G22*1000/($B$4*$E22),0))</f>
-        <v>1.15942028985507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3474,7 +3495,7 @@
         <v>56</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>19</v>
@@ -3483,11 +3504,11 @@
         <v>0.9</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G27" s="11" t="n">
         <f aca="false">C27*F27</f>
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="H27" s="11" t="n">
         <f aca="false">IF($D27="3F",$G27/3,IF($D27=H$9,$G27,0))</f>
@@ -3499,7 +3520,7 @@
       </c>
       <c r="J27" s="11" t="n">
         <f aca="false">IF($D27="3F",$G27/3,IF($D27=J$9,$G27,0))</f>
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="K27" s="12" t="n">
         <f aca="false">IF($D27="3F",$G27*1000/(3*$B$4*$E27),IF($D27=K$9,$G27*1000/($B$4*$E27),0))</f>
@@ -3511,7 +3532,7 @@
       </c>
       <c r="M27" s="12" t="n">
         <f aca="false">IF($D27="3F",$G27*1000/(3*$B$4*$E27),IF($D27=M$9,$G27*1000/($B$4*$E27),0))</f>
-        <v>2.60869565217391</v>
+        <v>1.44927536231884</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3618,20 +3639,20 @@
         <v>62</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G30" s="11" t="n">
         <f aca="false">C30*F30</f>
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H30" s="11" t="n">
         <f aca="false">IF($D30="3F",$G30/3,IF($D30=H$9,$G30,0))</f>
@@ -3639,11 +3660,11 @@
       </c>
       <c r="I30" s="11" t="n">
         <f aca="false">IF($D30="3F",$G30/3,IF($D30=I$9,$G30,0))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J30" s="11" t="n">
         <f aca="false">IF($D30="3F",$G30/3,IF($D30=J$9,$G30,0))</f>
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="K30" s="12" t="n">
         <f aca="false">IF($D30="3F",$G30*1000/(3*$B$4*$E30),IF($D30=K$9,$G30*1000/($B$4*$E30),0))</f>
@@ -3651,11 +3672,11 @@
       </c>
       <c r="L30" s="12" t="n">
         <f aca="false">IF($D30="3F",$G30*1000/(3*$B$4*$E30),IF($D30=L$9,$G30*1000/($B$4*$E30),0))</f>
-        <v>2.2883295194508</v>
+        <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
         <f aca="false">IF($D30="3F",$G30*1000/(3*$B$4*$E30),IF($D30=M$9,$G30*1000/($B$4*$E30),0))</f>
-        <v>0</v>
+        <v>2.60869565217391</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3666,10 +3687,10 @@
         <v>64</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>0.95</v>
@@ -3679,7 +3700,7 @@
       </c>
       <c r="G31" s="11" t="n">
         <f aca="false">C31*F31</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H31" s="11" t="n">
         <f aca="false">IF($D31="3F",$G31/3,IF($D31=H$9,$G31,0))</f>
@@ -3687,11 +3708,11 @@
       </c>
       <c r="I31" s="11" t="n">
         <f aca="false">IF($D31="3F",$G31/3,IF($D31=I$9,$G31,0))</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J31" s="11" t="n">
         <f aca="false">IF($D31="3F",$G31/3,IF($D31=J$9,$G31,0))</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <f aca="false">IF($D31="3F",$G31*1000/(3*$B$4*$E31),IF($D31=K$9,$G31*1000/($B$4*$E31),0))</f>
@@ -3699,11 +3720,11 @@
       </c>
       <c r="L31" s="12" t="n">
         <f aca="false">IF($D31="3F",$G31*1000/(3*$B$4*$E31),IF($D31=L$9,$G31*1000/($B$4*$E31),0))</f>
-        <v>0</v>
+        <v>2.2883295194508</v>
       </c>
       <c r="M31" s="12" t="n">
         <f aca="false">IF($D31="3F",$G31*1000/(3*$B$4*$E31),IF($D31=M$9,$G31*1000/($B$4*$E31),0))</f>
-        <v>1.37299771167048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3714,20 +3735,20 @@
         <v>66</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="11" t="n">
         <f aca="false">C32*F32</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H32" s="11" t="n">
         <f aca="false">IF($D32="3F",$G32/3,IF($D32=H$9,$G32,0))</f>
@@ -3735,7 +3756,7 @@
       </c>
       <c r="I32" s="11" t="n">
         <f aca="false">IF($D32="3F",$G32/3,IF($D32=I$9,$G32,0))</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J32" s="11" t="n">
         <f aca="false">IF($D32="3F",$G32/3,IF($D32=J$9,$G32,0))</f>
@@ -3747,7 +3768,7 @@
       </c>
       <c r="L32" s="12" t="n">
         <f aca="false">IF($D32="3F",$G32*1000/(3*$B$4*$E32),IF($D32=L$9,$G32*1000/($B$4*$E32),0))</f>
-        <v>0</v>
+        <v>1.37299771167048</v>
       </c>
       <c r="M32" s="12" t="n">
         <f aca="false">IF($D32="3F",$G32*1000/(3*$B$4*$E32),IF($D32=M$9,$G32*1000/($B$4*$E32),0))</f>
@@ -3756,16 +3777,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E33" s="9" t="n">
         <v>1</v>
@@ -3804,16 +3825,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>1</v>
@@ -3851,250 +3872,268 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="16" t="n">
-        <f aca="false">SUM(C10:C34)</f>
-        <v>58.75</v>
-      </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="16" t="n">
-        <f aca="false">SUM(G10:G34)</f>
-        <v>51.97</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <f aca="false">SUM(H10:H34)</f>
+      <c r="A35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <f aca="false">C35*F35</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <f aca="false">IF($D35="3F",$G35/3,IF($D35=H$9,$G35,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <f aca="false">IF($D35="3F",$G35/3,IF($D35=I$9,$G35,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <f aca="false">IF($D35="3F",$G35/3,IF($D35=J$9,$G35,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <f aca="false">IF($D35="3F",$G35*1000/(3*$B$4*$E35),IF($D35=K$9,$G35*1000/($B$4*$E35),0))</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <f aca="false">IF($D35="3F",$G35*1000/(3*$B$4*$E35),IF($D35=L$9,$G35*1000/($B$4*$E35),0))</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <f aca="false">IF($D35="3F",$G35*1000/(3*$B$4*$E35),IF($D35=M$9,$G35*1000/($B$4*$E35),0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="16" t="n">
+        <f aca="false">SUM(C10:C35)</f>
+        <v>59.05</v>
+      </c>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="16" t="n">
+        <f aca="false">SUM(G10:G35)</f>
+        <v>52.27</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <f aca="false">SUM(H10:H35)</f>
         <v>17.355</v>
       </c>
-      <c r="I35" s="16" t="n">
-        <f aca="false">SUM(I10:I34)</f>
-        <v>17.255</v>
-      </c>
-      <c r="J35" s="16" t="n">
-        <f aca="false">SUM(J10:J34)</f>
-        <v>17.36</v>
-      </c>
-      <c r="K35" s="17" t="n">
-        <f aca="false">SUM(K10:K34)</f>
+      <c r="I36" s="16" t="n">
+        <f aca="false">SUM(I10:I35)</f>
+        <v>17.54</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <f aca="false">SUM(J10:J35)</f>
+        <v>17.375</v>
+      </c>
+      <c r="K36" s="17" t="n">
+        <f aca="false">SUM(K10:K35)</f>
         <v>83.3320620391559</v>
       </c>
-      <c r="L35" s="17" t="n">
-        <f aca="false">SUM(L10:L34)</f>
-        <v>83.230358504958</v>
-      </c>
-      <c r="M35" s="17" t="n">
-        <f aca="false">SUM(M10:M34)</f>
-        <v>83.7884566488685</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="L36" s="17" t="n">
+        <f aca="false">SUM(L10:L35)</f>
+        <v>84.5308924485126</v>
+      </c>
+      <c r="M36" s="17" t="n">
+        <f aca="false">SUM(M10:M35)</f>
+        <v>83.9371980676328</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="18" t="n">
-        <f aca="false">C35</f>
-        <v>58.75</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B39" s="18" t="n">
-        <f aca="false">G35</f>
-        <v>51.97</v>
+        <f aca="false">C36</f>
+        <v>59.05</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="B40" s="18" t="n">
-        <f aca="false">(MAX(H35:J35)-MIN(H35:J35))/AVERAGE(H35:J35)*100</f>
-        <v>0.606118914758517</v>
+        <f aca="false">G36</f>
+        <v>52.27</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="19" t="str">
-        <f aca="false">IF(B40&lt;=10,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>74</v>
+      </c>
+      <c r="B41" s="18" t="n">
+        <f aca="false">(MAX(H36:J36)-MIN(H36:J36))/AVERAGE(H36:J36)*100</f>
+        <v>1.06179452841017</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="20" t="n">
-        <f aca="false">MAX(K35:M35)</f>
-        <v>83.7884566488685</v>
+        <v>75</v>
+      </c>
+      <c r="B42" s="19" t="str">
+        <f aca="false">IF(B41&lt;=10,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B43" s="20" t="n">
-        <f aca="false">AVERAGE(K35:M35)</f>
-        <v>83.4502923976608</v>
+        <f aca="false">MAX(K36:M36)</f>
+        <v>84.5308924485126</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B44" s="21" t="n">
-        <f aca="false">G35*1000/(SQRT(3)*B5*AVERAGE(K35:M35))</f>
-        <v>0.898885211414368</v>
+        <v>77</v>
+      </c>
+      <c r="B44" s="20" t="n">
+        <f aca="false">AVERAGE(K36:M36)</f>
+        <v>83.9333841851004</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B45" s="20" t="n">
-        <f aca="false">SQRT(3)*B5*AVERAGE(K35:M35)/1000</f>
-        <v>57.8160585356909</v>
+        <v>78</v>
+      </c>
+      <c r="B45" s="21" t="n">
+        <f aca="false">G36*1000/(SQRT(3)*B5*AVERAGE(K36:M36))</f>
+        <v>0.898870540713252</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="19" t="str">
-        <f aca="false">IF(B42&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>79</v>
+      </c>
+      <c r="B46" s="20" t="n">
+        <f aca="false">SQRT(3)*B5*AVERAGE(K36:M36)/1000</f>
+        <v>58.1507543439168</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B47" s="20" t="n">
-        <f aca="false">B45/250*100</f>
-        <v>23.1264234142764</v>
+        <v>80</v>
+      </c>
+      <c r="B47" s="19" t="str">
+        <f aca="false">IF(B43&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B48" s="20" t="n">
-        <f aca="false">B42*(1+B7/100)</f>
-        <v>104.735570811086</v>
+        <f aca="false">B46/250*100</f>
+        <v>23.2603017375667</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="19" t="str">
-        <f aca="false">IF(B48&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
-        <v>UYGUN</v>
+        <v>82</v>
+      </c>
+      <c r="B49" s="20" t="n">
+        <f aca="false">B43*(1+B7/100)</f>
+        <v>105.663615560641</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="20" t="n">
-        <f aca="false">(B6-B42)/B6*100</f>
-        <v>47.6322145944572</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="B50" s="19" t="str">
+        <f aca="false">IF(B49&lt;=B6,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B51" s="20" t="n">
+        <f aca="false">(B6-B43)/B6*100</f>
+        <v>47.1681922196796</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="7" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D54" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7" t="s">
+      <c r="E54" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="F54" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="G54" s="7"/>
+      <c r="H54" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="8" t="s">
+      <c r="I54" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="8" t="s">
+      <c r="J54" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="G54" s="8"/>
-      <c r="H54" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D55" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>94</v>
@@ -4104,7 +4143,7 @@
         <v>2</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="11" t="n">
         <v>0</v>
@@ -4112,10 +4151,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>95</v>
@@ -4124,10 +4163,10 @@
         <v>1.5</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="11" t="n">
@@ -4137,31 +4176,31 @@
         <v>1.5</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D57" s="23" t="n">
         <v>1.5</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="11" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I57" s="11" t="n">
         <v>1.5</v>
@@ -4172,29 +4211,29 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J58" s="11" t="n">
         <v>1.5</v>
@@ -4202,19 +4241,19 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="D59" s="23" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>99</v>
@@ -4227,27 +4266,27 @@
         <v>2.9</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D60" s="23" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>19</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="11" t="n">
@@ -4257,12 +4296,12 @@
         <v>2.9</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>3.12</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>61</v>
@@ -4271,20 +4310,20 @@
         <v>62</v>
       </c>
       <c r="D61" s="23" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J61" s="11" t="n">
         <v>3.12</v>
@@ -4292,22 +4331,22 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D62" s="23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="11" t="n">
@@ -4317,34 +4356,34 @@
         <v>3.4</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D63" s="23" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J63" s="11" t="n">
         <v>3.52</v>
@@ -4352,26 +4391,26 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D64" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G64" s="8"/>
       <c r="H64" s="11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I64" s="11" t="n">
         <v>3.7</v>
@@ -4382,22 +4421,22 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D65" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="11" t="n">
@@ -4407,34 +4446,34 @@
         <v>3.7</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="D66" s="23" t="n">
-        <v>0.255</v>
+        <v>0.3</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="11" t="n">
         <v>3.8</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>3.955</v>
+        <v>3.7</v>
       </c>
       <c r="J66" s="11" t="n">
         <v>3.82</v>
@@ -4442,29 +4481,29 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D67" s="23" t="n">
-        <v>0.255</v>
+        <v>0.3</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="11" t="n">
-        <v>4.055</v>
+        <v>3.8</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>3.955</v>
+        <v>4</v>
       </c>
       <c r="J67" s="11" t="n">
         <v>3.82</v>
@@ -4472,45 +4511,104 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D68" s="23" t="n">
-        <v>0.24</v>
+        <v>0.255</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="11" t="n">
         <v>4.055</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>3.955</v>
+        <v>4</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>4.06</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>106</v>
       </c>
+      <c r="D69" s="23" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G69" s="8"/>
+      <c r="H69" s="11" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>4.075</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G70" s="8"/>
+      <c r="H70" s="11" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>4.075</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="K8:M8"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="F56:G56"/>
     <mergeCell ref="F57:G57"/>
@@ -4525,6 +4623,8 @@
     <mergeCell ref="F66:G66"/>
     <mergeCell ref="F67:G67"/>
     <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F70:G70"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4541,7 +4641,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
@@ -4571,7 +4671,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4579,12 +4679,12 @@
         <v>1</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4592,21 +4692,21 @@
         <v>44</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4672,7 +4772,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4694,7 +4794,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4716,7 +4816,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4738,7 +4838,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4760,7 +4860,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4810,70 +4910,70 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="W14" s="12" t="n">
         <v>95</v>
@@ -4888,39 +4988,39 @@
         <v>216</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E15" s="11" t="n">
-        <f aca="false">'Yük Dengesi'!B39</f>
-        <v>51.97</v>
+        <f aca="false">'Yük Dengesi'!B40</f>
+        <v>52.27</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="23" t="n">
-        <f aca="false">'Yük Dengesi'!B44</f>
-        <v>0.898885211414368</v>
+        <f aca="false">'Yük Dengesi'!B45</f>
+        <v>0.898870540713252</v>
       </c>
       <c r="H15" s="12" t="n">
-        <f aca="false">'Yük Dengesi'!B42</f>
-        <v>83.7884566488685</v>
+        <f aca="false">'Yük Dengesi'!B43</f>
+        <v>84.5308924485126</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J15" s="27" t="n">
         <v>95</v>
@@ -4929,10 +5029,10 @@
         <v>30</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>160</v>
@@ -4947,18 +5047,18 @@
       </c>
       <c r="Q15" s="11" t="n">
         <f aca="false">IF(F15="3F",SQRT(3),2)*H15*K15*AA15*(G15/($D$3*J15)+($D$4/1000)*SQRT(1-G15^2))</f>
-        <v>1.08887519301945</v>
+        <v>1.09851869654788</v>
       </c>
       <c r="R15" s="11" t="n">
         <f aca="false">Q15/IF(F15="3F",$D$5,$D$6)*100</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="S15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="11" t="n">
         <f aca="false">R15+S15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="U15" s="11" t="n">
         <f aca="false">$D$11</f>
@@ -4974,7 +5074,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
@@ -4983,7 +5083,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
@@ -4999,7 +5099,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J16" s="27" t="n">
         <v>4</v>
@@ -5008,10 +5108,10 @@
         <v>25</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>14</v>
@@ -5034,11 +5134,11 @@
       </c>
       <c r="S16" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T16" s="11" t="n">
         <f aca="false">R16+S16</f>
-        <v>0.897905480308557</v>
+        <v>0.900316356190664</v>
       </c>
       <c r="U16" s="11" t="n">
         <f aca="false">IF(D16="aydınlatma",$D$10,$D$9)</f>
@@ -5054,7 +5154,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>23</v>
@@ -5063,7 +5163,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
@@ -5079,7 +5179,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J17" s="27" t="n">
         <v>4</v>
@@ -5088,10 +5188,10 @@
         <v>25</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>14</v>
@@ -5114,11 +5214,11 @@
       </c>
       <c r="S17" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T17" s="11" t="n">
         <f aca="false">R17+S17</f>
-        <v>0.897905480308557</v>
+        <v>0.900316356190664</v>
       </c>
       <c r="U17" s="11" t="n">
         <f aca="false">IF(D17="aydınlatma",$D$10,$D$9)</f>
@@ -5134,7 +5234,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
@@ -5143,7 +5243,7 @@
         <v>26</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
@@ -5159,7 +5259,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J18" s="27" t="n">
         <v>4</v>
@@ -5168,10 +5268,10 @@
         <v>25</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>14</v>
@@ -5194,11 +5294,11 @@
       </c>
       <c r="S18" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T18" s="11" t="n">
         <f aca="false">R18+S18</f>
-        <v>0.897905480308557</v>
+        <v>0.900316356190664</v>
       </c>
       <c r="U18" s="11" t="n">
         <f aca="false">IF(D18="aydınlatma",$D$10,$D$9)</f>
@@ -5214,7 +5314,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>27</v>
@@ -5223,7 +5323,7 @@
         <v>28</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
@@ -5239,7 +5339,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J19" s="27" t="n">
         <v>4</v>
@@ -5248,10 +5348,10 @@
         <v>25</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>14</v>
@@ -5274,11 +5374,11 @@
       </c>
       <c r="S19" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T19" s="11" t="n">
         <f aca="false">R19+S19</f>
-        <v>0.897905480308557</v>
+        <v>0.900316356190664</v>
       </c>
       <c r="U19" s="11" t="n">
         <f aca="false">IF(D19="aydınlatma",$D$10,$D$9)</f>
@@ -5294,7 +5394,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
@@ -5303,7 +5403,7 @@
         <v>30</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
@@ -5319,7 +5419,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J20" s="27" t="n">
         <v>4</v>
@@ -5328,10 +5428,10 @@
         <v>25</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>14</v>
@@ -5354,11 +5454,11 @@
       </c>
       <c r="S20" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T20" s="11" t="n">
         <f aca="false">R20+S20</f>
-        <v>0.897905480308557</v>
+        <v>0.900316356190664</v>
       </c>
       <c r="U20" s="11" t="n">
         <f aca="false">IF(D20="aydınlatma",$D$10,$D$9)</f>
@@ -5374,7 +5474,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>31</v>
@@ -5383,7 +5483,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
@@ -5399,7 +5499,7 @@
         <v>11.2262552342427</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J21" s="27" t="n">
         <v>4</v>
@@ -5408,10 +5508,10 @@
         <v>25</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>14</v>
@@ -5434,11 +5534,11 @@
       </c>
       <c r="S21" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T21" s="11" t="n">
         <f aca="false">R21+S21</f>
-        <v>0.897905480308557</v>
+        <v>0.900316356190664</v>
       </c>
       <c r="U21" s="11" t="n">
         <f aca="false">IF(D21="aydınlatma",$D$10,$D$9)</f>
@@ -5454,7 +5554,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>33</v>
@@ -5463,13 +5563,13 @@
         <v>34</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0.95</v>
@@ -5479,7 +5579,7 @@
         <v>9.1533180778032</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J22" s="27" t="n">
         <v>16</v>
@@ -5488,10 +5588,10 @@
         <v>100</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>16</v>
@@ -5514,11 +5614,11 @@
       </c>
       <c r="S22" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T22" s="11" t="n">
         <f aca="false">R22+S22</f>
-        <v>1.36616909985702</v>
+        <v>1.36857997573913</v>
       </c>
       <c r="U22" s="11" t="n">
         <f aca="false">IF(D22="aydınlatma",$D$10,$D$9)</f>
@@ -5534,7 +5634,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>35</v>
@@ -5543,13 +5643,13 @@
         <v>36</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0.9</v>
@@ -5559,7 +5659,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J23" s="27" t="n">
         <v>16</v>
@@ -5568,10 +5668,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>16</v>
@@ -5594,11 +5694,11 @@
       </c>
       <c r="S23" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T23" s="11" t="n">
         <f aca="false">R23+S23</f>
-        <v>2.47894895151244</v>
+        <v>2.48135982739455</v>
       </c>
       <c r="U23" s="11" t="n">
         <f aca="false">IF(D23="aydınlatma",$D$10,$D$9)</f>
@@ -5614,7 +5714,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>37</v>
@@ -5623,13 +5723,13 @@
         <v>38</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0.9</v>
@@ -5639,7 +5739,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J24" s="27" t="n">
         <v>16</v>
@@ -5648,10 +5748,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>16</v>
@@ -5674,11 +5774,11 @@
       </c>
       <c r="S24" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T24" s="11" t="n">
         <f aca="false">R24+S24</f>
-        <v>2.47894895151244</v>
+        <v>2.48135982739455</v>
       </c>
       <c r="U24" s="11" t="n">
         <f aca="false">IF(D24="aydınlatma",$D$10,$D$9)</f>
@@ -5694,7 +5794,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -5703,13 +5803,13 @@
         <v>40</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0.9</v>
@@ -5719,7 +5819,7 @@
         <v>14.4927536231884</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J25" s="27" t="n">
         <v>16</v>
@@ -5728,10 +5828,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>16</v>
@@ -5754,11 +5854,11 @@
       </c>
       <c r="S25" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T25" s="11" t="n">
         <f aca="false">R25+S25</f>
-        <v>2.47894895151244</v>
+        <v>2.48135982739455</v>
       </c>
       <c r="U25" s="11" t="n">
         <f aca="false">IF(D25="aydınlatma",$D$10,$D$9)</f>
@@ -5774,7 +5874,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>41</v>
@@ -5783,13 +5883,13 @@
         <v>42</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>0.255</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0.9</v>
@@ -5799,7 +5899,7 @@
         <v>1.23188405797101</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J26" s="27" t="n">
         <v>2.5</v>
@@ -5808,10 +5908,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>10</v>
@@ -5834,11 +5934,11 @@
       </c>
       <c r="S26" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T26" s="11" t="n">
         <f aca="false">R26+S26</f>
-        <v>1.44578501835342</v>
+        <v>1.44819589423553</v>
       </c>
       <c r="U26" s="11" t="n">
         <f aca="false">IF(D26="aydınlatma",$D$10,$D$9)</f>
@@ -5854,7 +5954,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>43</v>
@@ -5863,13 +5963,13 @@
         <v>44</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>0.255</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0.9</v>
@@ -5879,7 +5979,7 @@
         <v>1.23188405797101</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J27" s="27" t="n">
         <v>2.5</v>
@@ -5888,10 +5988,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>10</v>
@@ -5914,11 +6014,11 @@
       </c>
       <c r="S27" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T27" s="11" t="n">
         <f aca="false">R27+S27</f>
-        <v>1.44578501835342</v>
+        <v>1.44819589423553</v>
       </c>
       <c r="U27" s="11" t="n">
         <f aca="false">IF(D27="aydınlatma",$D$10,$D$9)</f>
@@ -5934,7 +6034,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>45</v>
@@ -5943,13 +6043,13 @@
         <v>46</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0.24</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0.9</v>
@@ -5959,7 +6059,7 @@
         <v>1.15942028985507</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>2.5</v>
@@ -5968,10 +6068,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>10</v>
@@ -5994,11 +6094,11 @@
       </c>
       <c r="S28" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T28" s="11" t="n">
         <f aca="false">R28+S28</f>
-        <v>1.3767517112888</v>
+        <v>1.3791625871709</v>
       </c>
       <c r="U28" s="11" t="n">
         <f aca="false">IF(D28="aydınlatma",$D$10,$D$9)</f>
@@ -6014,7 +6114,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>47</v>
@@ -6023,13 +6123,13 @@
         <v>48</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0.9</v>
@@ -6039,7 +6139,7 @@
         <v>1.93236714975845</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J29" s="27" t="n">
         <v>2.5</v>
@@ -6048,10 +6148,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>10</v>
@@ -6074,11 +6174,11 @@
       </c>
       <c r="S29" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T29" s="11" t="n">
         <f aca="false">R29+S29</f>
-        <v>0.732440845352336</v>
+        <v>0.734851721234443</v>
       </c>
       <c r="U29" s="11" t="n">
         <f aca="false">IF(D29="aydınlatma",$D$10,$D$9)</f>
@@ -6094,7 +6194,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>49</v>
@@ -6103,13 +6203,13 @@
         <v>50</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0.9</v>
@@ -6119,7 +6219,7 @@
         <v>1.44927536231884</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J30" s="27" t="n">
         <v>2.5</v>
@@ -6128,10 +6228,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>10</v>
@@ -6154,11 +6254,11 @@
       </c>
       <c r="S30" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T30" s="11" t="n">
         <f aca="false">R30+S30</f>
-        <v>0.617385333577967</v>
+        <v>0.619796209460074</v>
       </c>
       <c r="U30" s="11" t="n">
         <f aca="false">IF(D30="aydınlatma",$D$10,$D$9)</f>
@@ -6174,7 +6274,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>51</v>
@@ -6183,13 +6283,13 @@
         <v>52</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0.9</v>
@@ -6199,7 +6299,7 @@
         <v>1.44927536231884</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J31" s="27" t="n">
         <v>2.5</v>
@@ -6208,10 +6308,10 @@
         <v>66.6666666666667</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>10</v>
@@ -6234,11 +6334,11 @@
       </c>
       <c r="S31" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T31" s="11" t="n">
         <f aca="false">R31+S31</f>
-        <v>0.617385333577967</v>
+        <v>0.619796209460074</v>
       </c>
       <c r="U31" s="11" t="n">
         <f aca="false">IF(D31="aydınlatma",$D$10,$D$9)</f>
@@ -6254,7 +6354,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>53</v>
@@ -6263,13 +6363,13 @@
         <v>54</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.9</v>
@@ -6279,7 +6379,7 @@
         <v>6.76328502415459</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J32" s="27" t="n">
         <v>2.5</v>
@@ -6288,10 +6388,10 @@
         <v>28</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>10</v>
@@ -6314,11 +6414,11 @@
       </c>
       <c r="S32" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T32" s="11" t="n">
         <f aca="false">R32+S32</f>
-        <v>1.62527161672143</v>
+        <v>1.62768249260354</v>
       </c>
       <c r="U32" s="11" t="n">
         <f aca="false">IF(D32="aydınlatma",$D$10,$D$9)</f>
@@ -6334,7 +6434,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>55</v>
@@ -6343,35 +6443,35 @@
         <v>56</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="H33" s="11" t="n">
         <f aca="false">IF(F33="3F",E33*1000/(SQRT(3)*$D$5*G33),E33*1000/($D$6*G33))</f>
-        <v>2.89855072463768</v>
+        <v>1.44927536231884</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>10</v>
@@ -6386,19 +6486,19 @@
       </c>
       <c r="Q33" s="11" t="n">
         <f aca="false">IF(F33="3F",SQRT(3),2)*H33*K33*AA33*(G33/($D$3*J33)+($D$4/1000)*SQRT(1-G33^2))</f>
-        <v>4.76329818745885</v>
+        <v>0.119082454686471</v>
       </c>
       <c r="R33" s="11" t="n">
         <f aca="false">Q33/IF(F33="3F",$D$5,$D$6)*100</f>
-        <v>2.07099921193863</v>
+        <v>0.0517749802984657</v>
       </c>
       <c r="S33" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T33" s="11" t="n">
         <f aca="false">R33+S33</f>
-        <v>2.34321801019349</v>
+        <v>0.326404654435435</v>
       </c>
       <c r="U33" s="11" t="n">
         <f aca="false">IF(D33="aydınlatma",$D$10,$D$9)</f>
@@ -6414,7 +6514,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>57</v>
@@ -6423,13 +6523,13 @@
         <v>58</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0.9</v>
@@ -6439,7 +6539,7 @@
         <v>2.89855072463768</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J34" s="27" t="n">
         <v>2.5</v>
@@ -6448,10 +6548,10 @@
         <v>100</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>10</v>
@@ -6474,11 +6574,11 @@
       </c>
       <c r="S34" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T34" s="11" t="n">
         <f aca="false">R34+S34</f>
-        <v>2.34321801019349</v>
+        <v>2.3456288860756</v>
       </c>
       <c r="U34" s="11" t="n">
         <f aca="false">IF(D34="aydınlatma",$D$10,$D$9)</f>
@@ -6494,7 +6594,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>59</v>
@@ -6503,13 +6603,13 @@
         <v>60</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E35" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0.9</v>
@@ -6519,7 +6619,7 @@
         <v>2.89855072463768</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J35" s="27" t="n">
         <v>2.5</v>
@@ -6528,10 +6628,10 @@
         <v>100</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>10</v>
@@ -6554,11 +6654,11 @@
       </c>
       <c r="S35" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T35" s="11" t="n">
         <f aca="false">R35+S35</f>
-        <v>2.34321801019349</v>
+        <v>2.3456288860756</v>
       </c>
       <c r="U35" s="11" t="n">
         <f aca="false">IF(D35="aydınlatma",$D$10,$D$9)</f>
@@ -6574,7 +6674,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>61</v>
@@ -6583,35 +6683,35 @@
         <v>62</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H36" s="11" t="n">
         <f aca="false">IF(F36="3F",E36*1000/(SQRT(3)*$D$5*G36),E36*1000/($D$6*G36))</f>
-        <v>2.2883295194508</v>
+        <v>2.89855072463768</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="J36" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="K36" s="27" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>10</v>
@@ -6626,23 +6726,23 @@
       </c>
       <c r="Q36" s="11" t="n">
         <f aca="false">IF(F36="3F",SQRT(3),2)*H36*K36*AA36*(G36/($D$3*J36)+($D$4/1000)*SQRT(1-G36^2))</f>
-        <v>1.38740058120139</v>
+        <v>4.76329818745885</v>
       </c>
       <c r="R36" s="11" t="n">
         <f aca="false">Q36/IF(F36="3F",$D$5,$D$6)*100</f>
-        <v>0.603217644000603</v>
+        <v>2.07099921193863</v>
       </c>
       <c r="S36" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T36" s="11" t="n">
         <f aca="false">R36+S36</f>
-        <v>0.875436442255466</v>
+        <v>2.3456288860756</v>
       </c>
       <c r="U36" s="11" t="n">
         <f aca="false">IF(D36="aydınlatma",$D$10,$D$9)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V36" s="24" t="str">
         <f aca="false">IF(AND(H36&lt;=N36,N36&lt;=P36,T36&lt;=U36),"UYGUN","UYGUN DEĞİL")</f>
@@ -6654,7 +6754,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>63</v>
@@ -6663,23 +6763,23 @@
         <v>64</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0.95</v>
       </c>
       <c r="H37" s="11" t="n">
         <f aca="false">IF(F37="3F",E37*1000/(SQRT(3)*$D$5*G37),E37*1000/($D$6*G37))</f>
-        <v>1.37299771167048</v>
+        <v>2.2883295194508</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J37" s="27" t="n">
         <v>2.5</v>
@@ -6688,10 +6788,10 @@
         <v>35</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>10</v>
@@ -6706,23 +6806,23 @@
       </c>
       <c r="Q37" s="11" t="n">
         <f aca="false">IF(F37="3F",SQRT(3),2)*H37*K37*AA37*(G37/($D$3*J37)+($D$4/1000)*SQRT(1-G37^2))</f>
-        <v>0.832440348720832</v>
+        <v>1.38740058120139</v>
       </c>
       <c r="R37" s="11" t="n">
         <f aca="false">Q37/IF(F37="3F",$D$5,$D$6)*100</f>
-        <v>0.361930586400362</v>
+        <v>0.603217644000603</v>
       </c>
       <c r="S37" s="11" t="n">
         <f aca="false">$R$15</f>
-        <v>0.272218798254863</v>
+        <v>0.27462967413697</v>
       </c>
       <c r="T37" s="11" t="n">
         <f aca="false">R37+S37</f>
-        <v>0.634149384655224</v>
+        <v>0.877847318137573</v>
       </c>
       <c r="U37" s="11" t="n">
         <f aca="false">IF(D37="aydınlatma",$D$10,$D$9)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V37" s="24" t="str">
         <f aca="false">IF(AND(H37&lt;=N37,N37&lt;=P37,T37&lt;=U37),"UYGUN","UYGUN DEĞİL")</f>
@@ -6732,14 +6832,94 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="s">
-        <v>179</v>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <f aca="false">IF(F38="3F",E38*1000/(SQRT(3)*$D$5*G38),E38*1000/($D$6*G38))</f>
+        <v>1.37299771167048</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <f aca="false">INDEX($X$4:$Z$14,MATCH(J38,$W$4:$W$14,0),MATCH(L38,$X$3:$Z$3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="P38" s="12" t="n">
+        <f aca="false">O38*IF(L38="D2-3",$D$8,$D$7)</f>
+        <v>19.2</v>
+      </c>
+      <c r="Q38" s="11" t="n">
+        <f aca="false">IF(F38="3F",SQRT(3),2)*H38*K38*AA38*(G38/($D$3*J38)+($D$4/1000)*SQRT(1-G38^2))</f>
+        <v>0.832440348720832</v>
+      </c>
+      <c r="R38" s="11" t="n">
+        <f aca="false">Q38/IF(F38="3F",$D$5,$D$6)*100</f>
+        <v>0.361930586400362</v>
+      </c>
+      <c r="S38" s="11" t="n">
+        <f aca="false">$R$15</f>
+        <v>0.27462967413697</v>
+      </c>
+      <c r="T38" s="11" t="n">
+        <f aca="false">R38+S38</f>
+        <v>0.636560260537331</v>
+      </c>
+      <c r="U38" s="11" t="n">
+        <f aca="false">IF(D38="aydınlatma",$D$10,$D$9)</f>
+        <v>3</v>
+      </c>
+      <c r="V38" s="24" t="str">
+        <f aca="false">IF(AND(H38&lt;=N38,N38&lt;=P38,T38&lt;=U38),"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="AA38" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>180</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -6769,7 +6949,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -6782,7 +6962,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6795,24 +6975,24 @@
         <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -6822,642 +7002,642 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>191</v>
-      </c>
       <c r="F7" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C8" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" s="22" t="s">
         <v>198</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C14" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C15" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C16" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C17" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C18" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C21" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C23" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C24" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C27" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C29" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C31" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C32" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C33" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C34" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C35" s="22" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C36" s="22" t="n">
         <v>6</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C37" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7465,79 +7645,79 @@
         <v>33</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C38" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C40" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C41" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7545,99 +7725,99 @@
         <v>53</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C42" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>297</v>
+        <v>55</v>
       </c>
       <c r="B43" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="C43" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>299</v>
-      </c>
       <c r="E43" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>287</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>59</v>
+        <v>301</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C44" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>301</v>
+        <v>61</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C45" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>195</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C46" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7648,36 +7828,36 @@
         <v>307</v>
       </c>
       <c r="C47" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>308</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>309</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="C48" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="C48" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D48" s="13" t="s">
+      <c r="E48" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F48" s="22" t="s">
         <v>312</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7688,16 +7868,16 @@
         <v>314</v>
       </c>
       <c r="C49" s="22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>315</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7708,16 +7888,16 @@
         <v>317</v>
       </c>
       <c r="C50" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>318</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7728,16 +7908,16 @@
         <v>320</v>
       </c>
       <c r="C51" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>321</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7754,10 +7934,10 @@
         <v>324</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7768,16 +7948,16 @@
         <v>326</v>
       </c>
       <c r="C53" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>327</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7788,63 +7968,63 @@
         <v>329</v>
       </c>
       <c r="C54" s="22" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>330</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
+      <c r="B55" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C55" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="C56" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="13" t="s">
+      <c r="A56" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="E56" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>336</v>
-      </c>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="28" t="s">
-        <v>140</v>
+        <v>335</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C57" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D57" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E57" s="22" t="s">
         <v>338</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>335</v>
       </c>
       <c r="F57" s="22" t="s">
         <v>339</v>
@@ -7852,22 +8032,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>340</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>341</v>
       </c>
       <c r="C58" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" s="22" t="s">
         <v>342</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7878,59 +8058,59 @@
         <v>344</v>
       </c>
       <c r="C59" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>345</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="C60" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="C60" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="13" t="s">
+      <c r="E60" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F60" s="22" t="s">
         <v>349</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>352</v>
       </c>
       <c r="C61" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F61" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="E61" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="F61" s="22" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="28" t="s">
         <v>354</v>
       </c>
@@ -7938,16 +8118,16 @@
         <v>355</v>
       </c>
       <c r="C62" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>356</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7964,50 +8144,50 @@
         <v>359</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F63" s="22" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="28" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="28" t="s">
+      <c r="B64" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="C64" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="C64" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>363</v>
-      </c>
       <c r="E64" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="B65" s="13" t="s">
-        <v>362</v>
-      </c>
       <c r="C65" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>365</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8015,39 +8195,39 @@
         <v>366</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C66" s="22" t="n">
         <v>10</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C67" s="22" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>370</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8055,19 +8235,19 @@
         <v>371</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C68" s="22" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>372</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8075,39 +8255,39 @@
         <v>373</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C69" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="28" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C70" s="22" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>377</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8115,19 +8295,19 @@
         <v>378</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C71" s="22" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>379</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8135,39 +8315,39 @@
         <v>380</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C72" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C73" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>384</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8175,19 +8355,19 @@
         <v>385</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C74" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>386</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8195,39 +8375,39 @@
         <v>387</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C75" s="22" t="n">
         <v>4</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="28" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C76" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>391</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8235,19 +8415,19 @@
         <v>392</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C77" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>393</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8255,205 +8435,265 @@
         <v>394</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C78" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="28" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C79" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="28" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C80" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>401</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
-        <v>155</v>
+        <v>402</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C81" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F81" s="22" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="28" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C82" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F82" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="28" t="s">
-        <v>405</v>
+        <v>157</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C83" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F83" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="28" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C84" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F84" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="28" t="s">
-        <v>171</v>
+        <v>411</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C85" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F85" s="22" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="28" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C86" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F86" s="22" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="28" t="s">
-        <v>412</v>
+        <v>173</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C87" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F87" s="22" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="C88" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="E88" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F88" s="22" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="C89" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="E89" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F89" s="22" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="C90" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="D87" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="E87" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="F87" s="22" t="s">
-        <v>346</v>
+      <c r="D90" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="E90" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="22" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:F56"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8486,7 +8726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8496,7 +8736,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -8508,36 +8748,36 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1</v>
@@ -8556,18 +8796,18 @@
         <v>17</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>10</v>
@@ -8586,18 +8826,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>10</v>
@@ -8616,18 +8856,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>10</v>
@@ -8646,18 +8886,18 @@
         <v>17</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>17</v>
@@ -8673,21 +8913,21 @@
         <v>41</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>17</v>
@@ -8703,21 +8943,21 @@
         <v>43</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>16</v>
@@ -8733,21 +8973,21 @@
         <v>45</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>4</v>
@@ -8766,18 +9006,18 @@
         <v>19</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>3</v>
@@ -8796,18 +9036,18 @@
         <v>18</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>3</v>
@@ -8826,18 +9066,18 @@
         <v>17</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>4</v>
@@ -8850,24 +9090,24 @@
         <v>600</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" s="22" t="s">
         <v>19</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>4</v>
@@ -8880,24 +9120,24 @@
         <v>600</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G17" s="22" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>4</v>
@@ -8910,21 +9150,21 @@
         <v>600</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18" s="22" t="s">
         <v>19</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="32" t="n">
@@ -8943,7 +9183,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -8956,10 +9196,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>1</v>
@@ -8973,18 +9213,18 @@
         <v>19</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
@@ -8998,18 +9238,18 @@
         <v>18</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>1</v>
@@ -9023,46 +9263,46 @@
         <v>17</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C25" s="33" t="n">
         <f aca="false">ROUNDUP(('Kablo Çizelgesi'!K29+'Kablo Çizelgesi'!K30+'Kablo Çizelgesi'!K31)*(1+$C$3/100),0)</f>
         <v>220</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="22" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>1</v>
@@ -9070,16 +9310,16 @@
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -9115,7 +9355,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9125,7 +9365,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -9134,7 +9374,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="n">
@@ -9143,7 +9383,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="n">
@@ -9152,7 +9392,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="n">
@@ -9161,7 +9401,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="n">
@@ -9170,7 +9410,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="n">
@@ -9179,7 +9419,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="n">
@@ -9188,7 +9428,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="n">
@@ -9197,7 +9437,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="n">
@@ -9206,7 +9446,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="n">
@@ -9215,7 +9455,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="n">
@@ -9224,7 +9464,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="n">
@@ -9233,7 +9473,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="n">
@@ -9242,7 +9482,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="n">
@@ -9251,7 +9491,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="n">
@@ -9260,7 +9500,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="n">
@@ -9269,7 +9509,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="n">
@@ -9278,7 +9518,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="n">
@@ -9287,7 +9527,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
@@ -9296,7 +9536,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="n">
@@ -9305,7 +9545,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="n">
@@ -9314,7 +9554,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="n">
@@ -9323,7 +9563,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="n">
@@ -9335,516 +9575,516 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D28" s="33" t="n">
         <f aca="false">2*(($C$3+2*$C$5)+($C$4+2*$C$5))</f>
         <v>88</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D29" s="33" t="n">
         <f aca="false">ROUNDUP(D28*(1+$C$10/100),0)</f>
         <v>97</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D30" s="33" t="n">
         <f aca="false">2*(ROUNDUP(($C$3+2*$C$5)/$C$8,0)+ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>12</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D31" s="33" t="n">
         <f aca="false">D30*$C$7</f>
         <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">MAX(($C$3+2*$C$5)/ROUNDUP(($C$3+2*$C$5)/$C$8,0),($C$4+2*$C$5)/ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>7.33333333333333</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D33" s="33" t="n">
         <f aca="false">$C$15</f>
         <v>4</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D34" s="33" t="n">
         <f aca="false">MIN(8,MAX(2,ROUNDUP(2*($C$3+$C$4)/$C$9,0)))</f>
         <v>6</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D35" s="33" t="n">
         <f aca="false">D34</f>
         <v>6</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D36" s="33" t="n">
         <f aca="false">ROUNDUP((D34*($C$11+$C$6)+($C$13-$C$11)+(PI()*$C$14/2+2))*(1+$C$10/100),0)</f>
         <v>101</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D37" s="33" t="n">
         <f aca="false">ROUNDUP((2*($C$3+$C$4)+$C$4/2+3)*(1+$C$10/100),0)</f>
         <v>103</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D38" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">$C$23+$C$24+$C$25</f>
         <v>4.5</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="F39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D40" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D41" s="33" t="n">
         <f aca="false">ROUNDUP($C$16*(1+$C$10/100),0)</f>
         <v>3</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D42" s="33" t="n">
         <f aca="false">ROUNDUP($C$17*(1+$C$10/100),0)</f>
         <v>4</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D43" s="33" t="n">
         <f aca="false">ROUNDUP($C$22*(1+$C$10/100),0)</f>
         <v>33</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D44" s="33" t="n">
         <f aca="false">$C$18</f>
         <v>3</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D45" s="33" t="n">
         <f aca="false">($C$18-1)*$C$19+6</f>
         <v>18</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D46" s="33" t="n">
         <f aca="false">ROUNDUP($C$21*$C$20*(1+$C$10/100),0)</f>
         <v>80</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D48" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
         <v>27</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D50" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D51" s="33" t="n">
         <f aca="false">ROUNDUP(D49/10,0)</f>
         <v>3</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -9906,7 +10146,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9916,7 +10156,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9936,7 +10176,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9946,7 +10186,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -9956,7 +10196,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -9966,7 +10206,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -9976,7 +10216,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -9986,7 +10226,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -9996,7 +10236,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -10016,7 +10256,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -10026,7 +10266,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -10036,7 +10276,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -10046,7 +10286,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -10056,7 +10296,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -10066,7 +10306,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -10076,7 +10316,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10086,7 +10326,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -10096,7 +10336,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -10110,7 +10350,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -10119,12 +10359,12 @@
         <v>360.843918243516</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -10133,12 +10373,12 @@
         <v>9.0210979560879</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -10147,12 +10387,12 @@
         <v>0.0256</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -10161,12 +10401,12 @@
         <v>0.00832</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -10175,12 +10415,12 @@
         <v>0.0242102788088035</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -10189,12 +10429,12 @@
         <v>0.0056390977443609</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -10203,12 +10443,12 @@
         <v>0.0024</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -10217,12 +10457,12 @@
         <v>0.0300493485473292</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -10231,12 +10471,12 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -10250,52 +10490,52 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">$D$12</f>
         <v>160</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F35" s="22" t="n">
         <f aca="false">$D$14</f>
@@ -10314,21 +10554,21 @@
         <v>UYGUN</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">$D$15</f>
@@ -10351,24 +10591,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>63</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F37" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -10386,24 +10626,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>25</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F38" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -10421,27 +10661,27 @@
         <v>UYGUN</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="D39" s="22" t="n">
         <v>25</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G39" s="22" t="n">
         <v>10</v>
@@ -10455,18 +10695,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>63</v>
@@ -10489,24 +10729,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F41" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -10527,16 +10767,16 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="E42" s="22" t="n">
         <v>30</v>
@@ -10556,18 +10796,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="D43" s="22" t="n">
         <v>25</v>
@@ -10590,24 +10830,24 @@
         <v>UYGUN</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>10</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F44" s="22" t="n">
         <f aca="false">$D$19</f>
@@ -10625,15 +10865,15 @@
         <v>UYGUN</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="G45" s="8" t="n">
         <f aca="false">$D$10</f>
@@ -10650,7 +10890,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -10664,42 +10904,42 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C49" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10734,10 +10974,10 @@
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="C50" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10772,10 +11012,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C51" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10810,7 +11050,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -10824,29 +11064,29 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -10855,15 +11095,15 @@
         <v>960</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -10872,19 +11112,19 @@
         <v>100</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="F56" s="24" t="str">
         <f aca="false">IF(D56&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -10893,19 +11133,19 @@
         <v>10</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="F57" s="24" t="str">
         <f aca="false">IF(D57&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -10914,20 +11154,20 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -8127,7 +8127,7 @@
         <v>338</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -3343,7 +3343,7 @@
         <v>1.93236714975845</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>49</v>
       </c>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Kablo Çizelgesi" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Pano Malzeme Listesi" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Aydınlatma ve Priz Envanteri" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Topraklama ve Yıldırım Malzeme" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Kesici Selektivite" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Ses Sistemi Özeti" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Topraklama ve Yıldırım Malzeme" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Kesici Selektivite" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="690">
   <si>
     <t xml:space="preserve">YÜK DENGESİ VE FAZ DENGESİZLİĞİ</t>
   </si>
@@ -1412,6 +1413,93 @@
   </si>
   <si>
     <t xml:space="preserve">Çizim 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SES SİSTEMİ ÖZETİ (hoparlör, güç kablosu, ses kablosu; Çizim 1 ve Çizim 6 ile aynı pozlar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kol / hat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoparlör poz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoparlör adedi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kol gücü (W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koruma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Güç kablosu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Güç kablosu L (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔU sonuç</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SES kablosu poz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses kablosu tipi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses kablosu L (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses kablosu sipariş (m, fire dahil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS1 · sağ kol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W19: NYY 3x2,5 mm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x1,5 mm² ekranlı (LiYCY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS2 · sol kol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20: NYY 3x2,5 mm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS3 · minare kol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W21: NYY 3x2,5 mm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM1 · AMF1 amfi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W18: NYY 3x2,5 mm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK1–SK3 (çıkışlar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amfi çıkışları → kol hoparlörleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not: Kol gücü hoparlörlere eşit bölünmüştür; amfi gücü, ses kablosu tipi ve boyları varsayımdır (sarı hücreler PARAMETRELER'den gelir). Güç kablosu uzunluğu ve ΔU değerleri 'Kablo Çizelgesi' sayfasından alınır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ses kablosu (SK) boyları ilgili kol güç kablosu boyuyla aynı alınmıştır (varsayım); amfi çıkış tipi ve hoparlör empedans uyumu üretici verisiyle doğrulanmalıdır.</t>
   </si>
   <si>
     <t xml:space="preserve">TOPRAKLAMA VE YILDIRIMDAN KORUNMA MALZEMESİ (metraj formüllerle)</t>
@@ -2166,7 +2254,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2301,6 +2389,10 @@
     </xf>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3343,7 +3435,7 @@
         <v>1.93236714975845</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
@@ -9342,6 +9434,385 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <f aca="false">IF(C6&gt;0,E6/C6,0)</f>
+        <v>150</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <f aca="false">'Kablo Çizelgesi'!E34*1000</f>
+        <v>600</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <f aca="false">'Kablo Çizelgesi'!K34</f>
+        <v>100</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!T34</f>
+        <v>2.3456288860756</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!U34</f>
+        <v>3</v>
+      </c>
+      <c r="L6" s="24" t="str">
+        <f aca="false">IF(J6&lt;=K6,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="M6" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="O6" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" s="30" t="n">
+        <f aca="false">ROUNDUP(O6*(1+$C$3/100),0)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <f aca="false">IF(C7&gt;0,E7/C7,0)</f>
+        <v>150</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <f aca="false">'Kablo Çizelgesi'!E35*1000</f>
+        <v>600</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <f aca="false">'Kablo Çizelgesi'!K35</f>
+        <v>100</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!T35</f>
+        <v>2.3456288860756</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!U35</f>
+        <v>3</v>
+      </c>
+      <c r="L7" s="24" t="str">
+        <f aca="false">IF(J7&lt;=K7,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="O7" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" s="30" t="n">
+        <f aca="false">ROUNDUP(O7*(1+$C$3/100),0)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <f aca="false">IF(C8&gt;0,E8/C8,0)</f>
+        <v>150</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <f aca="false">'Kablo Çizelgesi'!E36*1000</f>
+        <v>600</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <f aca="false">'Kablo Çizelgesi'!K36</f>
+        <v>100</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!T36</f>
+        <v>2.3456288860756</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!U36</f>
+        <v>3</v>
+      </c>
+      <c r="L8" s="24" t="str">
+        <f aca="false">IF(J8&lt;=K8,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="O8" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" s="30" t="n">
+        <f aca="false">ROUNDUP(O8*(1+$C$3/100),0)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <f aca="false">E9/C9</f>
+        <v>300</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <f aca="false">'Kablo Çizelgesi'!E33*1000</f>
+        <v>300</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <f aca="false">'Kablo Çizelgesi'!K33</f>
+        <v>5</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!T33</f>
+        <v>0.326404654435435</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <f aca="false">'Kablo Çizelgesi'!U33</f>
+        <v>3</v>
+      </c>
+      <c r="L9" s="24" t="str">
+        <f aca="false">IF(J9&lt;=K9,"UYGUN","UYGUN DEĞİL")</f>
+        <v>UYGUN</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="O9" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="P9" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="32" t="n">
+        <f aca="false">SUM(C6:C8)</f>
+        <v>12</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="32" t="n">
+        <f aca="false">SUM(E6:E9)</f>
+        <v>2100</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="17" t="n">
+        <f aca="false">SUM(I6:I9)</f>
+        <v>305</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="17" t="n">
+        <f aca="false">SUM(O6:O8)</f>
+        <v>300</v>
+      </c>
+      <c r="P10" s="32" t="n">
+        <f aca="false">SUM(P6:P8)</f>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -9355,7 +9826,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9365,7 +9836,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="n">
@@ -9374,7 +9845,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="n">
@@ -9383,7 +9854,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="n">
@@ -9392,7 +9863,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>492</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="n">
@@ -9401,7 +9872,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="n">
@@ -9410,7 +9881,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>465</v>
+        <v>494</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="n">
@@ -9419,7 +9890,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="n">
@@ -9428,7 +9899,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>467</v>
+        <v>496</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="n">
@@ -9437,7 +9908,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>468</v>
+        <v>497</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="n">
@@ -9446,7 +9917,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="n">
@@ -9455,7 +9926,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="n">
@@ -9464,7 +9935,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="n">
@@ -9473,7 +9944,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>472</v>
+        <v>501</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="n">
@@ -9482,7 +9953,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>473</v>
+        <v>502</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="n">
@@ -9491,7 +9962,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>474</v>
+        <v>503</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="n">
@@ -9500,7 +9971,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>475</v>
+        <v>504</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="n">
@@ -9509,7 +9980,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="n">
@@ -9518,7 +9989,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>477</v>
+        <v>506</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="n">
@@ -9527,7 +9998,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>478</v>
+        <v>507</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
@@ -9536,7 +10007,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="n">
@@ -9545,7 +10016,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>480</v>
+        <v>509</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="n">
@@ -9554,7 +10025,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="n">
@@ -9563,7 +10034,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>482</v>
+        <v>511</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="n">
@@ -9575,16 +10046,16 @@
         <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>485</v>
+        <v>514</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>187</v>
@@ -9592,10 +10063,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>452</v>
@@ -9605,18 +10076,18 @@
         <v>88</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>489</v>
+        <v>518</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>490</v>
+        <v>519</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>491</v>
+        <v>520</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>452</v>
@@ -9626,39 +10097,39 @@
         <v>97</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>492</v>
+        <v>521</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>490</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>493</v>
+        <v>522</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>494</v>
+        <v>523</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D30" s="33" t="n">
         <f aca="false">2*(ROUNDUP(($C$3+2*$C$5)/$C$8,0)+ROUNDUP(($C$4+2*$C$5)/$C$8,0))</f>
         <v>12</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>497</v>
+        <v>526</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>493</v>
+        <v>522</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>498</v>
+        <v>527</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>452</v>
@@ -9668,16 +10139,16 @@
         <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>499</v>
+        <v>528</v>
       </c>
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>493</v>
+        <v>522</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>452</v>
@@ -9687,81 +10158,81 @@
         <v>7.33333333333333</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>501</v>
+        <v>530</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>504</v>
+        <v>533</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D33" s="33" t="n">
         <f aca="false">$C$15</f>
         <v>4</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>505</v>
+        <v>534</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>506</v>
+        <v>535</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D34" s="33" t="n">
         <f aca="false">MIN(8,MAX(2,ROUNDUP(2*($C$3+$C$4)/$C$9,0)))</f>
         <v>6</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>509</v>
+        <v>538</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>511</v>
+        <v>540</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D35" s="33" t="n">
         <f aca="false">D34</f>
         <v>6</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>515</v>
+        <v>544</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>452</v>
@@ -9771,18 +10242,18 @@
         <v>101</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>519</v>
+        <v>548</v>
       </c>
       <c r="C37" s="22" t="s">
         <v>452</v>
@@ -9792,39 +10263,39 @@
         <v>103</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>521</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D38" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>452</v>
@@ -9834,37 +10305,37 @@
         <v>4.5</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="F39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D40" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>531</v>
+        <v>560</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>532</v>
+        <v>561</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="C41" s="22" t="s">
         <v>452</v>
@@ -9874,18 +10345,18 @@
         <v>3</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>535</v>
+        <v>564</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>536</v>
+        <v>565</v>
       </c>
       <c r="C42" s="22" t="s">
         <v>452</v>
@@ -9895,10 +10366,10 @@
         <v>4</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9906,7 +10377,7 @@
         <v>343</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>537</v>
+        <v>566</v>
       </c>
       <c r="C43" s="22" t="s">
         <v>452</v>
@@ -9916,39 +10387,39 @@
         <v>33</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>538</v>
+        <v>567</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>539</v>
+        <v>568</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>541</v>
+        <v>570</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D44" s="33" t="n">
         <f aca="false">$C$18</f>
         <v>3</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>505</v>
+        <v>534</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="C45" s="22" t="s">
         <v>452</v>
@@ -9958,18 +10429,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>545</v>
+        <v>574</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>547</v>
+        <v>576</v>
       </c>
       <c r="C46" s="22" t="s">
         <v>452</v>
@@ -9979,94 +10450,94 @@
         <v>80</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>549</v>
+        <v>578</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>552</v>
+        <v>581</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D48" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>557</v>
+        <v>586</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>558</v>
+        <v>587</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
         <v>27</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>560</v>
+        <v>589</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>557</v>
+        <v>586</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D50" s="33" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>563</v>
+        <v>592</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10074,17 +10545,17 @@
         <v>69</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>564</v>
+        <v>593</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="D51" s="33" t="n">
         <f aca="false">ROUNDUP(D49/10,0)</f>
         <v>3</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -10124,7 +10595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -10146,7 +10617,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>566</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10156,7 +10627,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -10176,7 +10647,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -10186,7 +10657,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -10196,7 +10667,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>570</v>
+        <v>599</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -10206,7 +10677,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -10226,7 +10697,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -10236,7 +10707,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -10256,7 +10727,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -10266,7 +10737,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -10276,7 +10747,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -10286,7 +10757,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -10296,7 +10767,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -10306,7 +10777,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>579</v>
+        <v>608</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -10316,7 +10787,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10326,7 +10797,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>581</v>
+        <v>610</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -10336,7 +10807,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -10350,7 +10821,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>583</v>
+        <v>612</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -10359,12 +10830,12 @@
         <v>360.843918243516</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>584</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>585</v>
+        <v>614</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -10373,96 +10844,96 @@
         <v>9.0210979560879</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="35" t="n">
         <f aca="false">$D$5/100*$D$4^2/($D$3*1000)</f>
         <v>0.0256</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="35" t="n">
         <f aca="false">$D$6/100*$D$4^2/($D$3*1000)</f>
         <v>0.00832</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="34" t="n">
+      <c r="D27" s="35" t="n">
         <f aca="false">SQRT($D$25^2-$D$26^2)</f>
         <v>0.0242102788088035</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="34" t="n">
+      <c r="D28" s="35" t="n">
         <f aca="false">$D$7/(56*$D$8)</f>
         <v>0.0056390977443609</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="35" t="n">
         <f aca="false">$D$9/1000*$D$7</f>
         <v>0.0024</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="35" t="n">
         <f aca="false">SQRT(($D$26+$D$28)^2+($D$27+$D$29)^2)</f>
         <v>0.0300493485473292</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -10471,12 +10942,12 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -10490,31 +10961,31 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>600</v>
+        <v>629</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>428</v>
@@ -10522,13 +10993,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="B35" s="28" t="s">
         <v>143</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>605</v>
+        <v>634</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">$D$12</f>
@@ -10554,18 +11025,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>606</v>
+        <v>635</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>202</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>608</v>
+        <v>637</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>69</v>
@@ -10591,18 +11062,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>609</v>
+        <v>638</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>63</v>
@@ -10626,18 +11097,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>612</v>
+        <v>641</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="D38" s="22" t="n">
         <v>25</v>
@@ -10661,18 +11132,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>614</v>
+        <v>643</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>246</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="D39" s="22" t="n">
         <v>25</v>
@@ -10695,18 +11166,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>616</v>
+        <v>645</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>279</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>63</v>
@@ -10729,18 +11200,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>618</v>
+        <v>647</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="B41" s="28" t="s">
         <v>282</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>14</v>
@@ -10767,16 +11238,16 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>622</v>
+        <v>651</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="E42" s="22" t="n">
         <v>30</v>
@@ -10796,18 +11267,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>624</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="B43" s="28" t="s">
         <v>285</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>625</v>
+        <v>654</v>
       </c>
       <c r="D43" s="22" t="n">
         <v>25</v>
@@ -10830,18 +11301,18 @@
         <v>UYGUN</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>626</v>
+        <v>655</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>301</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>10</v>
@@ -10865,15 +11336,15 @@
         <v>UYGUN</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>629</v>
+        <v>658</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>630</v>
+        <v>659</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="G45" s="8" t="n">
         <f aca="false">$D$10</f>
@@ -10890,7 +11361,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -10904,34 +11375,34 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>636</v>
+        <v>665</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>637</v>
+        <v>666</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>639</v>
+        <v>668</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>640</v>
+        <v>669</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>642</v>
+        <v>671</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10939,7 +11410,7 @@
         <v>202</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>643</v>
+        <v>672</v>
       </c>
       <c r="C49" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -10977,7 +11448,7 @@
         <v>202</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>644</v>
+        <v>673</v>
       </c>
       <c r="C50" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -11015,7 +11486,7 @@
         <v>202</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="C51" s="8" t="n">
         <f aca="false">$D$15</f>
@@ -11050,7 +11521,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -11064,18 +11535,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>647</v>
+        <v>676</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -11086,7 +11557,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>650</v>
+        <v>679</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -11095,15 +11566,15 @@
         <v>960</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>584</v>
+        <v>613</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>651</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>652</v>
+        <v>681</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -11112,19 +11583,19 @@
         <v>100</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="F56" s="24" t="str">
         <f aca="false">IF(D56&gt;=$D$19+$D$18,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>654</v>
+        <v>683</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>655</v>
+        <v>684</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -11133,19 +11604,19 @@
         <v>10</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
       <c r="F57" s="24" t="str">
         <f aca="false">IF(D57&gt;=$D$31,"UYGUN","UYGUN DEĞİL")</f>
         <v>UYGUN</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>656</v>
+        <v>685</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>657</v>
+        <v>686</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -11154,20 +11625,20 @@
         <v>7.68536154160241</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>659</v>
+        <v>688</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>660</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">50 mm² Cu çıplak</t>
   </si>
   <si>
-    <t xml:space="preserve">EB1–EB6</t>
+    <t xml:space="preserve">EB1–EB8</t>
   </si>
   <si>
     <t xml:space="preserve">Eş potansiyel bağlantı iletkeni 16 mm² Cu (sarı-yeşil)</t>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="D46" s="33" t="n">
         <f aca="false">ROUNDUP($C$21*$C$20*(1+$C$10/100),0)</f>
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>577</v>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="D47" s="33" t="n">
         <f aca="false">$C$21</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>580</v>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D49" s="33" t="n">
         <f aca="false">D30+D34+2+1+$C$21</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>588</v>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>1.93236714975845</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>168</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>170</v>
       </c>

--- a/cikti/04_hesap_tablolari.xlsx
+++ b/cikti/04_hesap_tablolari.xlsx
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>1.93236714975845</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>168</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>170</v>
       </c>
